--- a/templates/_masters/TAX-006-home-office-allocator-DEMO.xlsx
+++ b/templates/_masters/TAX-006-home-office-allocator-DEMO.xlsx
@@ -34,7 +34,7 @@
     <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0"/>
     <numFmt numFmtId="166" formatCode="&quot;$&quot;0.00"/>
   </numFmts>
-  <fonts count="32">
+  <fonts count="33">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -58,6 +58,12 @@
       <i val="1"/>
       <color rgb="00C9A24B"/>
       <sz val="14"/>
+    </font>
+    <font>
+      <name val="Georgia"/>
+      <b val="1"/>
+      <color rgb="00C9A24B"/>
+      <sz val="16"/>
     </font>
     <font>
       <name val="Consolas"/>
@@ -482,7 +488,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="97">
+  <cellXfs count="98">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -497,233 +503,236 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" indent="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="17" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="3" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="21" fillId="3" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="20" fillId="3" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="21" fillId="3" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="20" fillId="3" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="21" fillId="3" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="21" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="22" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="7" fillId="7" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="8" fillId="7" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="8" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="1" fontId="7" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="1" fontId="8" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="1" fontId="7" fillId="7" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="1" fontId="8" fillId="7" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="10" fontId="10" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="10" fontId="11" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="3" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="21" fillId="3" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="15" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="16" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="23" fillId="2" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="24" fillId="2" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="165" fontId="9" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="10" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="23" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="7" fillId="7" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="8" fillId="7" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="165" fontId="7" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="8" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="165" fontId="7" fillId="7" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="8" fillId="7" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="165" fontId="22" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="23" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="11" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="23" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="23" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="165" fontId="10" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" indent="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center" indent="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="23" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="22" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="22" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="9" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="19" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="20" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="29" fillId="3" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="30" fillId="3" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="27" fillId="3" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="28" fillId="3" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="21" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="30" fillId="3" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="31" fillId="3" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="3" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="32" fillId="3" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="28" fillId="3" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="29" fillId="3" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="23" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="24" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="7" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="1" fontId="8" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="7" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="8" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="8" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="7" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="8" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1164,24 +1173,16 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="1" t="n"/>
-      <c r="B6" s="1" t="n"/>
-      <c r="C6" s="1" t="n"/>
-      <c r="D6" s="1" t="n"/>
-      <c r="E6" s="1" t="n"/>
-      <c r="F6" s="1" t="n"/>
-      <c r="G6" s="1" t="n"/>
-      <c r="H6" s="1" t="n"/>
-      <c r="I6" s="1" t="n"/>
-      <c r="J6" s="1" t="n"/>
-      <c r="K6" s="1" t="n"/>
-      <c r="L6" s="1" t="n"/>
+    <row r="6" ht="32" customHeight="1">
+      <c r="A6" s="5">
+        <f>IF(IFERROR('Launch'!A10,0)&gt;0,"✅  Home-office deduction = "&amp;TEXT('Launch'!A10,"$#,##0")&amp;"  ·  "&amp;'Launch'!E10&amp;" method.","📊  Fill Eligibility + Space Allocation to see your deduction.")</f>
+        <v/>
+      </c>
     </row>
     <row r="7" ht="22" customHeight="1">
-      <c r="A7" s="5" t="inlineStr">
-        <is>
-          <t>TAX-006 · v2.2 · DEMO</t>
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>TAX-006 · v2.3 · DEMO</t>
         </is>
       </c>
     </row>
@@ -1200,69 +1201,69 @@
       <c r="L8" s="1" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="6" t="n"/>
-      <c r="B10" s="6" t="n"/>
-      <c r="C10" s="6" t="n"/>
-      <c r="D10" s="6" t="n"/>
-      <c r="E10" s="6" t="n"/>
-      <c r="F10" s="6" t="n"/>
-      <c r="G10" s="6" t="n"/>
-      <c r="H10" s="6" t="n"/>
-      <c r="I10" s="6" t="n"/>
-      <c r="J10" s="6" t="n"/>
-      <c r="K10" s="6" t="n"/>
-      <c r="L10" s="6" t="n"/>
+      <c r="A10" s="7" t="n"/>
+      <c r="B10" s="7" t="n"/>
+      <c r="C10" s="7" t="n"/>
+      <c r="D10" s="7" t="n"/>
+      <c r="E10" s="7" t="n"/>
+      <c r="F10" s="7" t="n"/>
+      <c r="G10" s="7" t="n"/>
+      <c r="H10" s="7" t="n"/>
+      <c r="I10" s="7" t="n"/>
+      <c r="J10" s="7" t="n"/>
+      <c r="K10" s="7" t="n"/>
+      <c r="L10" s="7" t="n"/>
     </row>
     <row r="11" ht="28" customHeight="1">
-      <c r="A11" s="7" t="inlineStr">
+      <c r="A11" s="8" t="inlineStr">
         <is>
           <t>What you'll get</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="6" t="n"/>
-      <c r="B12" s="6" t="n"/>
-      <c r="C12" s="6" t="n"/>
-      <c r="D12" s="6" t="n"/>
-      <c r="E12" s="6" t="n"/>
-      <c r="F12" s="6" t="n"/>
-      <c r="G12" s="6" t="n"/>
-      <c r="H12" s="6" t="n"/>
-      <c r="I12" s="6" t="n"/>
-      <c r="J12" s="6" t="n"/>
-      <c r="K12" s="6" t="n"/>
-      <c r="L12" s="6" t="n"/>
+      <c r="A12" s="7" t="n"/>
+      <c r="B12" s="7" t="n"/>
+      <c r="C12" s="7" t="n"/>
+      <c r="D12" s="7" t="n"/>
+      <c r="E12" s="7" t="n"/>
+      <c r="F12" s="7" t="n"/>
+      <c r="G12" s="7" t="n"/>
+      <c r="H12" s="7" t="n"/>
+      <c r="I12" s="7" t="n"/>
+      <c r="J12" s="7" t="n"/>
+      <c r="K12" s="7" t="n"/>
+      <c r="L12" s="7" t="n"/>
     </row>
     <row r="13" ht="22" customHeight="1">
-      <c r="A13" s="8" t="inlineStr">
+      <c r="A13" s="9" t="inlineStr">
         <is>
           <t>📐 BUSINESS-USE %</t>
         </is>
       </c>
-      <c r="E13" s="8" t="inlineStr">
+      <c r="E13" s="9" t="inlineStr">
         <is>
           <t>⚖ METHOD COMPARE</t>
         </is>
       </c>
-      <c r="I13" s="8" t="inlineStr">
+      <c r="I13" s="9" t="inlineStr">
         <is>
           <t>📄 FORM 8829</t>
         </is>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">
-      <c r="A14" s="9" t="inlineStr">
+      <c r="A14" s="10" t="inlineStr">
         <is>
           <t>Your office sqft as a % of total home — drives every indirect expense.</t>
         </is>
       </c>
-      <c r="E14" s="9" t="inlineStr">
+      <c r="E14" s="10" t="inlineStr">
         <is>
           <t>Simplified ($5/sqft, max $1,500) vs Actual side-by-side, recommend the better one.</t>
         </is>
       </c>
-      <c r="I14" s="9" t="inlineStr">
+      <c r="I14" s="10" t="inlineStr">
         <is>
           <t>Print-ready Form 8829 mirror — Schedule E line 18a or Schedule C line 30.</t>
         </is>
@@ -1273,299 +1274,299 @@
     <row r="17" ht="22" customHeight="1"/>
     <row r="18" ht="22" customHeight="1"/>
     <row r="19">
-      <c r="A19" s="6" t="n"/>
-      <c r="B19" s="6" t="n"/>
-      <c r="C19" s="6" t="n"/>
-      <c r="D19" s="6" t="n"/>
-      <c r="E19" s="6" t="n"/>
-      <c r="F19" s="6" t="n"/>
-      <c r="G19" s="6" t="n"/>
-      <c r="H19" s="6" t="n"/>
-      <c r="I19" s="6" t="n"/>
-      <c r="J19" s="6" t="n"/>
-      <c r="K19" s="6" t="n"/>
-      <c r="L19" s="6" t="n"/>
+      <c r="A19" s="7" t="n"/>
+      <c r="B19" s="7" t="n"/>
+      <c r="C19" s="7" t="n"/>
+      <c r="D19" s="7" t="n"/>
+      <c r="E19" s="7" t="n"/>
+      <c r="F19" s="7" t="n"/>
+      <c r="G19" s="7" t="n"/>
+      <c r="H19" s="7" t="n"/>
+      <c r="I19" s="7" t="n"/>
+      <c r="J19" s="7" t="n"/>
+      <c r="K19" s="7" t="n"/>
+      <c r="L19" s="7" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="6" t="n"/>
-      <c r="B20" s="6" t="n"/>
-      <c r="C20" s="6" t="n"/>
-      <c r="D20" s="6" t="n"/>
-      <c r="E20" s="6" t="n"/>
-      <c r="F20" s="6" t="n"/>
-      <c r="G20" s="6" t="n"/>
-      <c r="H20" s="6" t="n"/>
-      <c r="I20" s="6" t="n"/>
-      <c r="J20" s="6" t="n"/>
-      <c r="K20" s="6" t="n"/>
-      <c r="L20" s="6" t="n"/>
+      <c r="A20" s="7" t="n"/>
+      <c r="B20" s="7" t="n"/>
+      <c r="C20" s="7" t="n"/>
+      <c r="D20" s="7" t="n"/>
+      <c r="E20" s="7" t="n"/>
+      <c r="F20" s="7" t="n"/>
+      <c r="G20" s="7" t="n"/>
+      <c r="H20" s="7" t="n"/>
+      <c r="I20" s="7" t="n"/>
+      <c r="J20" s="7" t="n"/>
+      <c r="K20" s="7" t="n"/>
+      <c r="L20" s="7" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="10" t="n"/>
-      <c r="B22" s="10" t="n"/>
-      <c r="C22" s="10" t="n"/>
-      <c r="D22" s="10" t="n"/>
-      <c r="E22" s="10" t="n"/>
-      <c r="F22" s="10" t="n"/>
-      <c r="G22" s="10" t="n"/>
-      <c r="H22" s="10" t="n"/>
-      <c r="I22" s="10" t="n"/>
-      <c r="J22" s="10" t="n"/>
-      <c r="K22" s="10" t="n"/>
-      <c r="L22" s="10" t="n"/>
+      <c r="A22" s="11" t="n"/>
+      <c r="B22" s="11" t="n"/>
+      <c r="C22" s="11" t="n"/>
+      <c r="D22" s="11" t="n"/>
+      <c r="E22" s="11" t="n"/>
+      <c r="F22" s="11" t="n"/>
+      <c r="G22" s="11" t="n"/>
+      <c r="H22" s="11" t="n"/>
+      <c r="I22" s="11" t="n"/>
+      <c r="J22" s="11" t="n"/>
+      <c r="K22" s="11" t="n"/>
+      <c r="L22" s="11" t="n"/>
     </row>
     <row r="23" ht="24" customHeight="1">
-      <c r="A23" s="11" t="inlineStr">
+      <c r="A23" s="12" t="inlineStr">
         <is>
           <t>Quick Start — be done in 10 minutes</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="10" t="n"/>
-      <c r="B24" s="12" t="inlineStr">
+      <c r="A24" s="11" t="n"/>
+      <c r="B24" s="13" t="inlineStr">
         <is>
           <t>① Eligibility: regular + exclusive + principal place tests</t>
         </is>
       </c>
-      <c r="G24" s="10" t="n"/>
-      <c r="H24" s="12" t="inlineStr">
+      <c r="G24" s="11" t="n"/>
+      <c r="H24" s="13" t="inlineStr">
         <is>
           <t>④ Actual expenses: utilities, insurance, mortgage int., depreciation</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="10" t="n"/>
-      <c r="B25" s="12" t="inlineStr">
+      <c r="A25" s="11" t="n"/>
+      <c r="B25" s="13" t="inlineStr">
         <is>
           <t>② Measure: total home sqft, office sqft</t>
         </is>
       </c>
-      <c r="G25" s="10" t="n"/>
-      <c r="H25" s="12" t="inlineStr">
+      <c r="G25" s="11" t="n"/>
+      <c r="H25" s="13" t="inlineStr">
         <is>
           <t>⑤ Routing: Schedule E or Schedule C</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="10" t="n"/>
-      <c r="B26" s="12" t="inlineStr">
+      <c r="A26" s="11" t="n"/>
+      <c r="B26" s="13" t="inlineStr">
         <is>
           <t>③ Method: Simplified or Actual</t>
         </is>
       </c>
-      <c r="G26" s="10" t="n"/>
-      <c r="H26" s="10" t="n"/>
-      <c r="I26" s="10" t="n"/>
-      <c r="J26" s="10" t="n"/>
-      <c r="K26" s="10" t="n"/>
-      <c r="L26" s="10" t="n"/>
+      <c r="G26" s="11" t="n"/>
+      <c r="H26" s="11" t="n"/>
+      <c r="I26" s="11" t="n"/>
+      <c r="J26" s="11" t="n"/>
+      <c r="K26" s="11" t="n"/>
+      <c r="L26" s="11" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="10" t="n"/>
-      <c r="B27" s="10" t="n"/>
-      <c r="C27" s="10" t="n"/>
-      <c r="D27" s="10" t="n"/>
-      <c r="E27" s="10" t="n"/>
-      <c r="F27" s="10" t="n"/>
-      <c r="G27" s="10" t="n"/>
-      <c r="H27" s="10" t="n"/>
-      <c r="I27" s="10" t="n"/>
-      <c r="J27" s="10" t="n"/>
-      <c r="K27" s="10" t="n"/>
-      <c r="L27" s="10" t="n"/>
+      <c r="A27" s="11" t="n"/>
+      <c r="B27" s="11" t="n"/>
+      <c r="C27" s="11" t="n"/>
+      <c r="D27" s="11" t="n"/>
+      <c r="E27" s="11" t="n"/>
+      <c r="F27" s="11" t="n"/>
+      <c r="G27" s="11" t="n"/>
+      <c r="H27" s="11" t="n"/>
+      <c r="I27" s="11" t="n"/>
+      <c r="J27" s="11" t="n"/>
+      <c r="K27" s="11" t="n"/>
+      <c r="L27" s="11" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="10" t="n"/>
-      <c r="B28" s="10" t="n"/>
-      <c r="C28" s="10" t="n"/>
-      <c r="D28" s="10" t="n"/>
-      <c r="E28" s="10" t="n"/>
-      <c r="F28" s="10" t="n"/>
-      <c r="G28" s="10" t="n"/>
-      <c r="H28" s="10" t="n"/>
-      <c r="I28" s="10" t="n"/>
-      <c r="J28" s="10" t="n"/>
-      <c r="K28" s="10" t="n"/>
-      <c r="L28" s="10" t="n"/>
+      <c r="A28" s="11" t="n"/>
+      <c r="B28" s="11" t="n"/>
+      <c r="C28" s="11" t="n"/>
+      <c r="D28" s="11" t="n"/>
+      <c r="E28" s="11" t="n"/>
+      <c r="F28" s="11" t="n"/>
+      <c r="G28" s="11" t="n"/>
+      <c r="H28" s="11" t="n"/>
+      <c r="I28" s="11" t="n"/>
+      <c r="J28" s="11" t="n"/>
+      <c r="K28" s="11" t="n"/>
+      <c r="L28" s="11" t="n"/>
     </row>
     <row r="30" ht="22" customHeight="1">
-      <c r="A30" s="13">
+      <c r="A30" s="14">
         <f>HYPERLINK("#'Eligibility'!A5", "GET STARTED — CHECK ELIGIBILITY  →")</f>
         <v/>
       </c>
-      <c r="B30" s="14" t="n"/>
-      <c r="C30" s="14" t="n"/>
-      <c r="D30" s="14" t="n"/>
-      <c r="E30" s="14" t="n"/>
-      <c r="F30" s="14" t="n"/>
-      <c r="G30" s="14" t="n"/>
-      <c r="H30" s="14" t="n"/>
-      <c r="I30" s="14" t="n"/>
-      <c r="J30" s="14" t="n"/>
-      <c r="K30" s="14" t="n"/>
-      <c r="L30" s="14" t="n"/>
+      <c r="B30" s="15" t="n"/>
+      <c r="C30" s="15" t="n"/>
+      <c r="D30" s="15" t="n"/>
+      <c r="E30" s="15" t="n"/>
+      <c r="F30" s="15" t="n"/>
+      <c r="G30" s="15" t="n"/>
+      <c r="H30" s="15" t="n"/>
+      <c r="I30" s="15" t="n"/>
+      <c r="J30" s="15" t="n"/>
+      <c r="K30" s="15" t="n"/>
+      <c r="L30" s="15" t="n"/>
     </row>
     <row r="31" ht="22" customHeight="1">
-      <c r="A31" s="14" t="n"/>
-      <c r="B31" s="14" t="n"/>
-      <c r="C31" s="14" t="n"/>
-      <c r="D31" s="14" t="n"/>
-      <c r="E31" s="14" t="n"/>
-      <c r="F31" s="14" t="n"/>
-      <c r="G31" s="14" t="n"/>
-      <c r="H31" s="14" t="n"/>
-      <c r="I31" s="14" t="n"/>
-      <c r="J31" s="14" t="n"/>
-      <c r="K31" s="14" t="n"/>
-      <c r="L31" s="14" t="n"/>
+      <c r="A31" s="15" t="n"/>
+      <c r="B31" s="15" t="n"/>
+      <c r="C31" s="15" t="n"/>
+      <c r="D31" s="15" t="n"/>
+      <c r="E31" s="15" t="n"/>
+      <c r="F31" s="15" t="n"/>
+      <c r="G31" s="15" t="n"/>
+      <c r="H31" s="15" t="n"/>
+      <c r="I31" s="15" t="n"/>
+      <c r="J31" s="15" t="n"/>
+      <c r="K31" s="15" t="n"/>
+      <c r="L31" s="15" t="n"/>
     </row>
     <row r="32" ht="22" customHeight="1">
-      <c r="A32" s="14" t="n"/>
-      <c r="B32" s="14" t="n"/>
-      <c r="C32" s="14" t="n"/>
-      <c r="D32" s="14" t="n"/>
-      <c r="E32" s="14" t="n"/>
-      <c r="F32" s="14" t="n"/>
-      <c r="G32" s="14" t="n"/>
-      <c r="H32" s="14" t="n"/>
-      <c r="I32" s="14" t="n"/>
-      <c r="J32" s="14" t="n"/>
-      <c r="K32" s="14" t="n"/>
-      <c r="L32" s="14" t="n"/>
+      <c r="A32" s="15" t="n"/>
+      <c r="B32" s="15" t="n"/>
+      <c r="C32" s="15" t="n"/>
+      <c r="D32" s="15" t="n"/>
+      <c r="E32" s="15" t="n"/>
+      <c r="F32" s="15" t="n"/>
+      <c r="G32" s="15" t="n"/>
+      <c r="H32" s="15" t="n"/>
+      <c r="I32" s="15" t="n"/>
+      <c r="J32" s="15" t="n"/>
+      <c r="K32" s="15" t="n"/>
+      <c r="L32" s="15" t="n"/>
     </row>
     <row r="33" ht="22" customHeight="1">
-      <c r="A33" s="14" t="n"/>
-      <c r="B33" s="14" t="n"/>
-      <c r="C33" s="14" t="n"/>
-      <c r="D33" s="14" t="n"/>
-      <c r="E33" s="14" t="n"/>
-      <c r="F33" s="14" t="n"/>
-      <c r="G33" s="14" t="n"/>
-      <c r="H33" s="14" t="n"/>
-      <c r="I33" s="14" t="n"/>
-      <c r="J33" s="14" t="n"/>
-      <c r="K33" s="14" t="n"/>
-      <c r="L33" s="14" t="n"/>
+      <c r="A33" s="15" t="n"/>
+      <c r="B33" s="15" t="n"/>
+      <c r="C33" s="15" t="n"/>
+      <c r="D33" s="15" t="n"/>
+      <c r="E33" s="15" t="n"/>
+      <c r="F33" s="15" t="n"/>
+      <c r="G33" s="15" t="n"/>
+      <c r="H33" s="15" t="n"/>
+      <c r="I33" s="15" t="n"/>
+      <c r="J33" s="15" t="n"/>
+      <c r="K33" s="15" t="n"/>
+      <c r="L33" s="15" t="n"/>
     </row>
     <row r="36">
-      <c r="A36" s="15" t="inlineStr">
+      <c r="A36" s="16" t="inlineStr">
         <is>
           <t>Progress:</t>
         </is>
       </c>
-      <c r="G36" s="16">
+      <c r="G36" s="17">
         <f>TEXT((COUNTA('Eligibility'!B8:B12) + COUNTA('Space Allocation'!B8:B11) + COUNTA('Method Election'!B8) + COUNTA('Actual Expenses'!B8:B17) + COUNTA('STR Routing'!B8))/21,"0%") &amp; " complete"</f>
         <v/>
       </c>
     </row>
     <row r="38" ht="18" customHeight="1">
-      <c r="A38" s="17" t="inlineStr">
+      <c r="A38" s="18" t="inlineStr">
         <is>
           <t>① Eligibility</t>
         </is>
       </c>
-      <c r="G38" s="18">
+      <c r="G38" s="19">
         <f>IF(COUNTA('Eligibility'!B8:B12)=5,"✅ Done",IF(COUNTA('Eligibility'!B8:B12)=0,"⏳ Empty","⏳ "&amp;COUNTA('Eligibility'!B8:B12)&amp;" of 5"))</f>
         <v/>
       </c>
-      <c r="K38" s="19">
+      <c r="K38" s="20">
         <f>HYPERLINK("#'Eligibility'!A5","→ go")</f>
         <v/>
       </c>
     </row>
     <row r="39" ht="18" customHeight="1">
-      <c r="A39" s="17" t="inlineStr">
+      <c r="A39" s="18" t="inlineStr">
         <is>
           <t>② Space Allocation</t>
         </is>
       </c>
-      <c r="G39" s="18">
+      <c r="G39" s="19">
         <f>IF(COUNTA('Space Allocation'!B8:B11)=4,"✅ Done",IF(COUNTA('Space Allocation'!B8:B11)=0,"⏳ Empty","⏳ "&amp;COUNTA('Space Allocation'!B8:B11)&amp;" of 4"))</f>
         <v/>
       </c>
-      <c r="K39" s="19">
+      <c r="K39" s="20">
         <f>HYPERLINK("#'Space Allocation'!A5","→ go")</f>
         <v/>
       </c>
     </row>
     <row r="40" ht="18" customHeight="1">
-      <c r="A40" s="17" t="inlineStr">
+      <c r="A40" s="18" t="inlineStr">
         <is>
           <t>③ Method Election</t>
         </is>
       </c>
-      <c r="G40" s="18">
+      <c r="G40" s="19">
         <f>IF(COUNTA('Method Election'!B8)=1,"✅ Done",IF(COUNTA('Method Election'!B8)=0,"⏳ Empty","⏳ "&amp;COUNTA('Method Election'!B8)&amp;" of 1"))</f>
         <v/>
       </c>
-      <c r="K40" s="19">
+      <c r="K40" s="20">
         <f>HYPERLINK("#'Method Election'!A5","→ go")</f>
         <v/>
       </c>
     </row>
     <row r="41" ht="18" customHeight="1">
-      <c r="A41" s="17" t="inlineStr">
+      <c r="A41" s="18" t="inlineStr">
         <is>
           <t>④ Actual Expenses</t>
         </is>
       </c>
-      <c r="G41" s="18">
+      <c r="G41" s="19">
         <f>IF(COUNTA('Actual Expenses'!B8:B17)=10,"✅ Done",IF(COUNTA('Actual Expenses'!B8:B17)=0,"⏳ Empty","⏳ "&amp;COUNTA('Actual Expenses'!B8:B17)&amp;" of 10"))</f>
         <v/>
       </c>
-      <c r="K41" s="19">
+      <c r="K41" s="20">
         <f>HYPERLINK("#'Actual Expenses'!A5","→ go")</f>
         <v/>
       </c>
     </row>
     <row r="42" ht="18" customHeight="1">
-      <c r="A42" s="17" t="inlineStr">
+      <c r="A42" s="18" t="inlineStr">
         <is>
           <t>⑤ STR Routing</t>
         </is>
       </c>
-      <c r="G42" s="18">
+      <c r="G42" s="19">
         <f>IF(COUNTA('STR Routing'!B8)=1,"✅ Done",IF(COUNTA('STR Routing'!B8)=0,"⏳ Empty","⏳ "&amp;COUNTA('STR Routing'!B8)&amp;" of 1"))</f>
         <v/>
       </c>
-      <c r="K42" s="19">
+      <c r="K42" s="20">
         <f>HYPERLINK("#'STR Routing'!A5","→ go")</f>
         <v/>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="20" t="n"/>
-      <c r="B47" s="20" t="n"/>
-      <c r="C47" s="20" t="n"/>
-      <c r="D47" s="20" t="n"/>
-      <c r="E47" s="20" t="n"/>
-      <c r="F47" s="20" t="n"/>
-      <c r="G47" s="20" t="n"/>
-      <c r="H47" s="20" t="n"/>
-      <c r="I47" s="20" t="n"/>
-      <c r="J47" s="20" t="n"/>
-      <c r="K47" s="20" t="n"/>
-      <c r="L47" s="20" t="n"/>
+      <c r="A47" s="21" t="n"/>
+      <c r="B47" s="21" t="n"/>
+      <c r="C47" s="21" t="n"/>
+      <c r="D47" s="21" t="n"/>
+      <c r="E47" s="21" t="n"/>
+      <c r="F47" s="21" t="n"/>
+      <c r="G47" s="21" t="n"/>
+      <c r="H47" s="21" t="n"/>
+      <c r="I47" s="21" t="n"/>
+      <c r="J47" s="21" t="n"/>
+      <c r="K47" s="21" t="n"/>
+      <c r="L47" s="21" t="n"/>
     </row>
     <row r="48" ht="18" customHeight="1">
-      <c r="A48" s="21" t="inlineStr">
+      <c r="A48" s="22" t="inlineStr">
         <is>
           <t>Questions? hello@thestrledger.com</t>
         </is>
       </c>
     </row>
     <row r="49" ht="18" customHeight="1">
-      <c r="A49" s="22" t="inlineStr">
+      <c r="A49" s="23" t="inlineStr">
         <is>
           <t>TAX-006 · v2.2 · Free updates forever</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="37">
+  <mergeCells count="38">
     <mergeCell ref="A41:F41"/>
     <mergeCell ref="A7:L7"/>
     <mergeCell ref="B25:F25"/>
@@ -1602,6 +1603,7 @@
     <mergeCell ref="K38:L38"/>
     <mergeCell ref="A49:L49"/>
     <mergeCell ref="H24:L24"/>
+    <mergeCell ref="A6:L6"/>
     <mergeCell ref="B26:F26"/>
   </mergeCells>
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
@@ -1648,23 +1650,23 @@
       <c r="L1" s="1" t="n"/>
     </row>
     <row r="2" ht="28" customHeight="1">
-      <c r="A2" s="13">
+      <c r="A2" s="14">
         <f>HYPERLINK("#'Start'!A1", "← START")</f>
         <v/>
       </c>
-      <c r="B2" s="14" t="n"/>
-      <c r="C2" s="14" t="n"/>
-      <c r="D2" s="23" t="inlineStr">
+      <c r="B2" s="15" t="n"/>
+      <c r="C2" s="15" t="n"/>
+      <c r="D2" s="24" t="inlineStr">
         <is>
           <t>SECTION 1 OF 5</t>
         </is>
       </c>
-      <c r="J2" s="24">
+      <c r="J2" s="25">
         <f>HYPERLINK("#'Space Allocation'!A5", "NEXT →")</f>
         <v/>
       </c>
-      <c r="K2" s="25" t="n"/>
-      <c r="L2" s="25" t="n"/>
+      <c r="K2" s="26" t="n"/>
+      <c r="L2" s="26" t="n"/>
     </row>
     <row r="3" ht="6" customHeight="1">
       <c r="A3" s="1" t="n"/>
@@ -1681,183 +1683,183 @@
       <c r="L3" s="1" t="n"/>
     </row>
     <row r="4" ht="36" customHeight="1">
-      <c r="A4" s="26" t="inlineStr">
+      <c r="A4" s="27" t="inlineStr">
         <is>
           <t>Eligibility</t>
         </is>
       </c>
     </row>
     <row r="5" ht="18" customHeight="1">
-      <c r="A5" s="27" t="inlineStr">
+      <c r="A5" s="28" t="inlineStr">
         <is>
           <t>IRC §280A — pass all three core tests, or the deduction is zero.</t>
         </is>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="28" t="inlineStr">
+      <c r="A6" s="29" t="inlineStr">
         <is>
           <t>Fill the highlighted fields below.</t>
         </is>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1">
-      <c r="A7" s="29" t="inlineStr">
+      <c r="A7" s="30" t="inlineStr">
         <is>
           <t>ELIGIBILITY</t>
         </is>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
-      <c r="A8" s="30" t="inlineStr">
+      <c r="A8" s="31" t="inlineStr">
         <is>
           <t>Office space used REGULARLY for STR business?</t>
         </is>
       </c>
-      <c r="B8" s="31" t="inlineStr">
+      <c r="B8" s="32" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="C8" s="32" t="n"/>
-      <c r="D8" s="32" t="n"/>
-      <c r="E8" s="32" t="n"/>
-      <c r="F8" s="32" t="n"/>
-      <c r="G8" s="32" t="n"/>
-      <c r="H8" s="32" t="n"/>
-      <c r="I8" s="32" t="n"/>
-      <c r="J8" s="32" t="n"/>
-      <c r="K8" s="32" t="n"/>
-      <c r="L8" s="33" t="n"/>
+      <c r="C8" s="33" t="n"/>
+      <c r="D8" s="33" t="n"/>
+      <c r="E8" s="33" t="n"/>
+      <c r="F8" s="33" t="n"/>
+      <c r="G8" s="33" t="n"/>
+      <c r="H8" s="33" t="n"/>
+      <c r="I8" s="33" t="n"/>
+      <c r="J8" s="33" t="n"/>
+      <c r="K8" s="33" t="n"/>
+      <c r="L8" s="34" t="n"/>
     </row>
     <row r="9" ht="22" customHeight="1">
-      <c r="A9" s="34" t="inlineStr">
+      <c r="A9" s="35" t="inlineStr">
         <is>
           <t>Office space used EXCLUSIVELY for business?</t>
         </is>
       </c>
-      <c r="B9" s="35" t="inlineStr">
+      <c r="B9" s="36" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="C9" s="6" t="n"/>
-      <c r="D9" s="6" t="n"/>
-      <c r="E9" s="6" t="n"/>
-      <c r="F9" s="6" t="n"/>
-      <c r="G9" s="6" t="n"/>
-      <c r="H9" s="6" t="n"/>
-      <c r="I9" s="6" t="n"/>
-      <c r="J9" s="6" t="n"/>
-      <c r="K9" s="6" t="n"/>
-      <c r="L9" s="36" t="n"/>
+      <c r="C9" s="7" t="n"/>
+      <c r="D9" s="7" t="n"/>
+      <c r="E9" s="7" t="n"/>
+      <c r="F9" s="7" t="n"/>
+      <c r="G9" s="7" t="n"/>
+      <c r="H9" s="7" t="n"/>
+      <c r="I9" s="7" t="n"/>
+      <c r="J9" s="7" t="n"/>
+      <c r="K9" s="7" t="n"/>
+      <c r="L9" s="37" t="n"/>
     </row>
     <row r="10" ht="22" customHeight="1">
-      <c r="A10" s="34" t="inlineStr">
+      <c r="A10" s="35" t="inlineStr">
         <is>
           <t>Is this your PRINCIPAL PLACE of STR business?</t>
         </is>
       </c>
-      <c r="B10" s="35" t="inlineStr">
+      <c r="B10" s="36" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="C10" s="6" t="n"/>
-      <c r="D10" s="6" t="n"/>
-      <c r="E10" s="6" t="n"/>
-      <c r="F10" s="6" t="n"/>
-      <c r="G10" s="6" t="n"/>
-      <c r="H10" s="6" t="n"/>
-      <c r="I10" s="6" t="n"/>
-      <c r="J10" s="6" t="n"/>
-      <c r="K10" s="6" t="n"/>
-      <c r="L10" s="36" t="n"/>
+      <c r="C10" s="7" t="n"/>
+      <c r="D10" s="7" t="n"/>
+      <c r="E10" s="7" t="n"/>
+      <c r="F10" s="7" t="n"/>
+      <c r="G10" s="7" t="n"/>
+      <c r="H10" s="7" t="n"/>
+      <c r="I10" s="7" t="n"/>
+      <c r="J10" s="7" t="n"/>
+      <c r="K10" s="7" t="n"/>
+      <c r="L10" s="37" t="n"/>
     </row>
     <row r="11" ht="22" customHeight="1">
-      <c r="A11" s="34" t="inlineStr">
+      <c r="A11" s="35" t="inlineStr">
         <is>
           <t>Used for storage of inventory/samples (alt qualifier)?</t>
         </is>
       </c>
-      <c r="B11" s="35" t="inlineStr">
+      <c r="B11" s="36" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="C11" s="6" t="n"/>
-      <c r="D11" s="6" t="n"/>
-      <c r="E11" s="6" t="n"/>
-      <c r="F11" s="6" t="n"/>
-      <c r="G11" s="6" t="n"/>
-      <c r="H11" s="6" t="n"/>
-      <c r="I11" s="6" t="n"/>
-      <c r="J11" s="6" t="n"/>
-      <c r="K11" s="6" t="n"/>
-      <c r="L11" s="36" t="n"/>
+      <c r="C11" s="7" t="n"/>
+      <c r="D11" s="7" t="n"/>
+      <c r="E11" s="7" t="n"/>
+      <c r="F11" s="7" t="n"/>
+      <c r="G11" s="7" t="n"/>
+      <c r="H11" s="7" t="n"/>
+      <c r="I11" s="7" t="n"/>
+      <c r="J11" s="7" t="n"/>
+      <c r="K11" s="7" t="n"/>
+      <c r="L11" s="37" t="n"/>
     </row>
     <row r="12" ht="22" customHeight="1">
-      <c r="A12" s="37" t="inlineStr">
+      <c r="A12" s="38" t="inlineStr">
         <is>
           <t>Used for day-care services (alt qualifier)?</t>
         </is>
       </c>
-      <c r="B12" s="38" t="inlineStr">
+      <c r="B12" s="39" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="C12" s="39" t="n"/>
-      <c r="D12" s="39" t="n"/>
-      <c r="E12" s="39" t="n"/>
-      <c r="F12" s="39" t="n"/>
-      <c r="G12" s="39" t="n"/>
-      <c r="H12" s="39" t="n"/>
-      <c r="I12" s="39" t="n"/>
-      <c r="J12" s="39" t="n"/>
-      <c r="K12" s="39" t="n"/>
-      <c r="L12" s="40" t="n"/>
+      <c r="C12" s="40" t="n"/>
+      <c r="D12" s="40" t="n"/>
+      <c r="E12" s="40" t="n"/>
+      <c r="F12" s="40" t="n"/>
+      <c r="G12" s="40" t="n"/>
+      <c r="H12" s="40" t="n"/>
+      <c r="I12" s="40" t="n"/>
+      <c r="J12" s="40" t="n"/>
+      <c r="K12" s="40" t="n"/>
+      <c r="L12" s="41" t="n"/>
     </row>
     <row r="14" ht="36" customHeight="1">
-      <c r="A14" s="41" t="inlineStr">
+      <c r="A14" s="42" t="inlineStr">
         <is>
           <t>ⓘ Three-test rule (IRC §280A): the office must be used (1) regularly, (2) exclusively, and (3) as your principal place of business OR a place where you meet clients/customers OR a separate structure. STR managers typically qualify under 'principal place of business' if substantial admin work happens there and there's no other fixed location.</t>
         </is>
       </c>
     </row>
     <row r="16" ht="22" customHeight="1">
-      <c r="A16" s="42">
+      <c r="A16" s="43">
         <f>HYPERLINK("#'Start'!A1", "← Back: Start")</f>
         <v/>
       </c>
-      <c r="B16" s="43" t="n"/>
-      <c r="C16" s="43" t="n"/>
-      <c r="D16" s="43" t="n"/>
-      <c r="E16" s="43" t="n"/>
-      <c r="F16" s="43" t="n"/>
-      <c r="G16" s="42">
+      <c r="B16" s="44" t="n"/>
+      <c r="C16" s="44" t="n"/>
+      <c r="D16" s="44" t="n"/>
+      <c r="E16" s="44" t="n"/>
+      <c r="F16" s="44" t="n"/>
+      <c r="G16" s="43">
         <f>HYPERLINK("#'Space Allocation'!A5", "Next: Space Allocation →")</f>
         <v/>
       </c>
-      <c r="H16" s="43" t="n"/>
-      <c r="I16" s="43" t="n"/>
-      <c r="J16" s="43" t="n"/>
-      <c r="K16" s="43" t="n"/>
-      <c r="L16" s="43" t="n"/>
+      <c r="H16" s="44" t="n"/>
+      <c r="I16" s="44" t="n"/>
+      <c r="J16" s="44" t="n"/>
+      <c r="K16" s="44" t="n"/>
+      <c r="L16" s="44" t="n"/>
     </row>
     <row r="17" ht="22" customHeight="1">
-      <c r="A17" s="43" t="n"/>
-      <c r="B17" s="43" t="n"/>
-      <c r="C17" s="43" t="n"/>
-      <c r="D17" s="43" t="n"/>
-      <c r="E17" s="43" t="n"/>
-      <c r="F17" s="43" t="n"/>
-      <c r="G17" s="43" t="n"/>
-      <c r="H17" s="43" t="n"/>
-      <c r="I17" s="43" t="n"/>
-      <c r="J17" s="43" t="n"/>
-      <c r="K17" s="43" t="n"/>
-      <c r="L17" s="43" t="n"/>
+      <c r="A17" s="44" t="n"/>
+      <c r="B17" s="44" t="n"/>
+      <c r="C17" s="44" t="n"/>
+      <c r="D17" s="44" t="n"/>
+      <c r="E17" s="44" t="n"/>
+      <c r="F17" s="44" t="n"/>
+      <c r="G17" s="44" t="n"/>
+      <c r="H17" s="44" t="n"/>
+      <c r="I17" s="44" t="n"/>
+      <c r="J17" s="44" t="n"/>
+      <c r="K17" s="44" t="n"/>
+      <c r="L17" s="44" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="15">
@@ -1937,23 +1939,23 @@
       <c r="L1" s="1" t="n"/>
     </row>
     <row r="2" ht="28" customHeight="1">
-      <c r="A2" s="13">
+      <c r="A2" s="14">
         <f>HYPERLINK("#'Eligibility'!A5", "← BACK")</f>
         <v/>
       </c>
-      <c r="B2" s="14" t="n"/>
-      <c r="C2" s="14" t="n"/>
-      <c r="D2" s="23" t="inlineStr">
+      <c r="B2" s="15" t="n"/>
+      <c r="C2" s="15" t="n"/>
+      <c r="D2" s="24" t="inlineStr">
         <is>
           <t>SECTION 2 OF 5</t>
         </is>
       </c>
-      <c r="J2" s="24">
+      <c r="J2" s="25">
         <f>HYPERLINK("#'Method Election'!A5", "NEXT →")</f>
         <v/>
       </c>
-      <c r="K2" s="25" t="n"/>
-      <c r="L2" s="25" t="n"/>
+      <c r="K2" s="26" t="n"/>
+      <c r="L2" s="26" t="n"/>
     </row>
     <row r="3" ht="6" customHeight="1">
       <c r="A3" s="1" t="n"/>
@@ -1970,164 +1972,164 @@
       <c r="L3" s="1" t="n"/>
     </row>
     <row r="4" ht="36" customHeight="1">
-      <c r="A4" s="26" t="inlineStr">
+      <c r="A4" s="27" t="inlineStr">
         <is>
           <t>Space Allocation</t>
         </is>
       </c>
     </row>
     <row r="5" ht="18" customHeight="1">
-      <c r="A5" s="27" t="inlineStr">
+      <c r="A5" s="28" t="inlineStr">
         <is>
           <t>Square footage drives the indirect-expense allocation.</t>
         </is>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="28" t="inlineStr">
+      <c r="A6" s="29" t="inlineStr">
         <is>
           <t>Fill the highlighted fields below.</t>
         </is>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1">
-      <c r="A7" s="29" t="inlineStr">
+      <c r="A7" s="30" t="inlineStr">
         <is>
           <t>SPACE ALLOCATION</t>
         </is>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
-      <c r="A8" s="30" t="inlineStr">
+      <c r="A8" s="31" t="inlineStr">
         <is>
           <t>Total home square footage:</t>
         </is>
       </c>
-      <c r="B8" s="44" t="n">
+      <c r="B8" s="45" t="n">
         <v>2400</v>
       </c>
-      <c r="C8" s="32" t="n"/>
-      <c r="D8" s="32" t="n"/>
-      <c r="E8" s="32" t="n"/>
-      <c r="F8" s="32" t="n"/>
-      <c r="G8" s="32" t="n"/>
-      <c r="H8" s="32" t="n"/>
-      <c r="I8" s="32" t="n"/>
-      <c r="J8" s="32" t="n"/>
-      <c r="K8" s="32" t="n"/>
-      <c r="L8" s="33" t="n"/>
+      <c r="C8" s="33" t="n"/>
+      <c r="D8" s="33" t="n"/>
+      <c r="E8" s="33" t="n"/>
+      <c r="F8" s="33" t="n"/>
+      <c r="G8" s="33" t="n"/>
+      <c r="H8" s="33" t="n"/>
+      <c r="I8" s="33" t="n"/>
+      <c r="J8" s="33" t="n"/>
+      <c r="K8" s="33" t="n"/>
+      <c r="L8" s="34" t="n"/>
     </row>
     <row r="9" ht="22" customHeight="1">
-      <c r="A9" s="34" t="inlineStr">
+      <c r="A9" s="35" t="inlineStr">
         <is>
           <t>Office square footage (regular + exclusive):</t>
         </is>
       </c>
-      <c r="B9" s="45" t="n">
+      <c r="B9" s="46" t="n">
         <v>110</v>
       </c>
-      <c r="C9" s="6" t="n"/>
-      <c r="D9" s="6" t="n"/>
-      <c r="E9" s="6" t="n"/>
-      <c r="F9" s="6" t="n"/>
-      <c r="G9" s="6" t="n"/>
-      <c r="H9" s="6" t="n"/>
-      <c r="I9" s="6" t="n"/>
-      <c r="J9" s="6" t="n"/>
-      <c r="K9" s="6" t="n"/>
-      <c r="L9" s="36" t="n"/>
+      <c r="C9" s="7" t="n"/>
+      <c r="D9" s="7" t="n"/>
+      <c r="E9" s="7" t="n"/>
+      <c r="F9" s="7" t="n"/>
+      <c r="G9" s="7" t="n"/>
+      <c r="H9" s="7" t="n"/>
+      <c r="I9" s="7" t="n"/>
+      <c r="J9" s="7" t="n"/>
+      <c r="K9" s="7" t="n"/>
+      <c r="L9" s="37" t="n"/>
     </row>
     <row r="10" ht="22" customHeight="1">
-      <c r="A10" s="34" t="inlineStr">
+      <c r="A10" s="35" t="inlineStr">
         <is>
           <t>Total rooms in home (alt method):</t>
         </is>
       </c>
-      <c r="B10" s="46" t="n">
+      <c r="B10" s="47" t="n">
         <v>9</v>
       </c>
-      <c r="C10" s="6" t="n"/>
-      <c r="D10" s="6" t="n"/>
-      <c r="E10" s="6" t="n"/>
-      <c r="F10" s="6" t="n"/>
-      <c r="G10" s="6" t="n"/>
-      <c r="H10" s="6" t="n"/>
-      <c r="I10" s="6" t="n"/>
-      <c r="J10" s="6" t="n"/>
-      <c r="K10" s="6" t="n"/>
-      <c r="L10" s="36" t="n"/>
+      <c r="C10" s="7" t="n"/>
+      <c r="D10" s="7" t="n"/>
+      <c r="E10" s="7" t="n"/>
+      <c r="F10" s="7" t="n"/>
+      <c r="G10" s="7" t="n"/>
+      <c r="H10" s="7" t="n"/>
+      <c r="I10" s="7" t="n"/>
+      <c r="J10" s="7" t="n"/>
+      <c r="K10" s="7" t="n"/>
+      <c r="L10" s="37" t="n"/>
     </row>
     <row r="11" ht="22" customHeight="1">
-      <c r="A11" s="37" t="inlineStr">
+      <c r="A11" s="38" t="inlineStr">
         <is>
           <t>Rooms used for business (alt method):</t>
         </is>
       </c>
-      <c r="B11" s="47" t="n">
+      <c r="B11" s="48" t="n">
         <v>1</v>
       </c>
-      <c r="C11" s="39" t="n"/>
-      <c r="D11" s="39" t="n"/>
-      <c r="E11" s="39" t="n"/>
-      <c r="F11" s="39" t="n"/>
-      <c r="G11" s="39" t="n"/>
-      <c r="H11" s="39" t="n"/>
-      <c r="I11" s="39" t="n"/>
-      <c r="J11" s="39" t="n"/>
-      <c r="K11" s="39" t="n"/>
-      <c r="L11" s="40" t="n"/>
+      <c r="C11" s="40" t="n"/>
+      <c r="D11" s="40" t="n"/>
+      <c r="E11" s="40" t="n"/>
+      <c r="F11" s="40" t="n"/>
+      <c r="G11" s="40" t="n"/>
+      <c r="H11" s="40" t="n"/>
+      <c r="I11" s="40" t="n"/>
+      <c r="J11" s="40" t="n"/>
+      <c r="K11" s="40" t="n"/>
+      <c r="L11" s="41" t="n"/>
     </row>
     <row r="13" ht="24" customHeight="1">
-      <c r="A13" s="48" t="inlineStr">
+      <c r="A13" s="49" t="inlineStr">
         <is>
           <t>Business-use % (computed):</t>
         </is>
       </c>
-      <c r="B13" s="49">
+      <c r="B13" s="50">
         <f>IF(B8&gt;0,B9/B8,0)</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="36" customHeight="1">
-      <c r="A15" s="41" t="inlineStr">
+      <c r="A15" s="42" t="inlineStr">
         <is>
           <t>Business-use % above = office sqft ÷ total home sqft. The IRS also accepts rooms-based allocation if all rooms are roughly equal in size — less common for STR. When in doubt, use sqft.</t>
         </is>
       </c>
     </row>
     <row r="17" ht="22" customHeight="1">
-      <c r="A17" s="42">
+      <c r="A17" s="43">
         <f>HYPERLINK("#'Eligibility'!A5", "← Back: Eligibility")</f>
         <v/>
       </c>
-      <c r="B17" s="43" t="n"/>
-      <c r="C17" s="43" t="n"/>
-      <c r="D17" s="43" t="n"/>
-      <c r="E17" s="43" t="n"/>
-      <c r="F17" s="43" t="n"/>
-      <c r="G17" s="42">
+      <c r="B17" s="44" t="n"/>
+      <c r="C17" s="44" t="n"/>
+      <c r="D17" s="44" t="n"/>
+      <c r="E17" s="44" t="n"/>
+      <c r="F17" s="44" t="n"/>
+      <c r="G17" s="43">
         <f>HYPERLINK("#'Method Election'!A5", "Next: Method Election →")</f>
         <v/>
       </c>
-      <c r="H17" s="43" t="n"/>
-      <c r="I17" s="43" t="n"/>
-      <c r="J17" s="43" t="n"/>
-      <c r="K17" s="43" t="n"/>
-      <c r="L17" s="43" t="n"/>
+      <c r="H17" s="44" t="n"/>
+      <c r="I17" s="44" t="n"/>
+      <c r="J17" s="44" t="n"/>
+      <c r="K17" s="44" t="n"/>
+      <c r="L17" s="44" t="n"/>
     </row>
     <row r="18" ht="22" customHeight="1">
-      <c r="A18" s="43" t="n"/>
-      <c r="B18" s="43" t="n"/>
-      <c r="C18" s="43" t="n"/>
-      <c r="D18" s="43" t="n"/>
-      <c r="E18" s="43" t="n"/>
-      <c r="F18" s="43" t="n"/>
-      <c r="G18" s="43" t="n"/>
-      <c r="H18" s="43" t="n"/>
-      <c r="I18" s="43" t="n"/>
-      <c r="J18" s="43" t="n"/>
-      <c r="K18" s="43" t="n"/>
-      <c r="L18" s="43" t="n"/>
+      <c r="A18" s="44" t="n"/>
+      <c r="B18" s="44" t="n"/>
+      <c r="C18" s="44" t="n"/>
+      <c r="D18" s="44" t="n"/>
+      <c r="E18" s="44" t="n"/>
+      <c r="F18" s="44" t="n"/>
+      <c r="G18" s="44" t="n"/>
+      <c r="H18" s="44" t="n"/>
+      <c r="I18" s="44" t="n"/>
+      <c r="J18" s="44" t="n"/>
+      <c r="K18" s="44" t="n"/>
+      <c r="L18" s="44" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -2185,23 +2187,23 @@
       <c r="L1" s="1" t="n"/>
     </row>
     <row r="2" ht="28" customHeight="1">
-      <c r="A2" s="13">
+      <c r="A2" s="14">
         <f>HYPERLINK("#'Space Allocation'!A5", "← BACK")</f>
         <v/>
       </c>
-      <c r="B2" s="14" t="n"/>
-      <c r="C2" s="14" t="n"/>
-      <c r="D2" s="23" t="inlineStr">
+      <c r="B2" s="15" t="n"/>
+      <c r="C2" s="15" t="n"/>
+      <c r="D2" s="24" t="inlineStr">
         <is>
           <t>SECTION 3 OF 5</t>
         </is>
       </c>
-      <c r="J2" s="24">
+      <c r="J2" s="25">
         <f>HYPERLINK("#'Actual Expenses'!A5", "NEXT →")</f>
         <v/>
       </c>
-      <c r="K2" s="25" t="n"/>
-      <c r="L2" s="25" t="n"/>
+      <c r="K2" s="26" t="n"/>
+      <c r="L2" s="26" t="n"/>
     </row>
     <row r="3" ht="6" customHeight="1">
       <c r="A3" s="1" t="n"/>
@@ -2218,196 +2220,196 @@
       <c r="L3" s="1" t="n"/>
     </row>
     <row r="4" ht="36" customHeight="1">
-      <c r="A4" s="26" t="inlineStr">
+      <c r="A4" s="27" t="inlineStr">
         <is>
           <t>Method Election</t>
         </is>
       </c>
     </row>
     <row r="5" ht="18" customHeight="1">
-      <c r="A5" s="27" t="inlineStr">
+      <c r="A5" s="28" t="inlineStr">
         <is>
           <t>Simplified ($5/sqft cap $1,500) vs Actual.</t>
         </is>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="28" t="inlineStr">
+      <c r="A6" s="29" t="inlineStr">
         <is>
           <t>Fill the highlighted fields below.</t>
         </is>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1">
-      <c r="A7" s="29" t="inlineStr">
+      <c r="A7" s="30" t="inlineStr">
         <is>
           <t>METHOD ELECTION</t>
         </is>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
-      <c r="A8" s="50" t="inlineStr">
+      <c r="A8" s="51" t="inlineStr">
         <is>
           <t>Method:</t>
         </is>
       </c>
-      <c r="B8" s="51" t="inlineStr">
+      <c r="B8" s="52" t="inlineStr">
         <is>
           <t>Actual</t>
         </is>
       </c>
-      <c r="C8" s="52" t="n"/>
-      <c r="D8" s="52" t="n"/>
-      <c r="E8" s="52" t="n"/>
-      <c r="F8" s="52" t="n"/>
-      <c r="G8" s="52" t="n"/>
-      <c r="H8" s="52" t="n"/>
-      <c r="I8" s="52" t="n"/>
-      <c r="J8" s="52" t="n"/>
-      <c r="K8" s="52" t="n"/>
-      <c r="L8" s="53" t="n"/>
+      <c r="C8" s="53" t="n"/>
+      <c r="D8" s="53" t="n"/>
+      <c r="E8" s="53" t="n"/>
+      <c r="F8" s="53" t="n"/>
+      <c r="G8" s="53" t="n"/>
+      <c r="H8" s="53" t="n"/>
+      <c r="I8" s="53" t="n"/>
+      <c r="J8" s="53" t="n"/>
+      <c r="K8" s="53" t="n"/>
+      <c r="L8" s="54" t="n"/>
     </row>
     <row r="11" ht="20" customHeight="1">
-      <c r="A11" s="54" t="inlineStr"/>
-      <c r="B11" s="54" t="inlineStr">
+      <c r="A11" s="55" t="inlineStr"/>
+      <c r="B11" s="55" t="inlineStr">
         <is>
           <t>Simplified</t>
         </is>
       </c>
-      <c r="C11" s="54" t="inlineStr">
+      <c r="C11" s="55" t="inlineStr">
         <is>
           <t>Actual</t>
         </is>
       </c>
-      <c r="D11" s="54" t="inlineStr">
+      <c r="D11" s="55" t="inlineStr">
         <is>
           <t>Difference</t>
         </is>
       </c>
     </row>
     <row r="12" ht="20" customHeight="1">
-      <c r="A12" s="55" t="inlineStr">
+      <c r="A12" s="56" t="inlineStr">
         <is>
           <t>Deduction this year</t>
         </is>
       </c>
-      <c r="B12" s="56">
+      <c r="B12" s="57">
         <f>MIN('Space Allocation'!B9,300)*5</f>
         <v/>
       </c>
-      <c r="C12" s="56">
+      <c r="C12" s="57">
         <f>IF(B8="Actual",'Actual Expenses'!B22,0)</f>
         <v/>
       </c>
-      <c r="D12" s="56">
+      <c r="D12" s="57">
         <f>C12-B12</f>
         <v/>
       </c>
     </row>
     <row r="13" ht="20" customHeight="1">
-      <c r="A13" s="55" t="inlineStr">
+      <c r="A13" s="56" t="inlineStr">
         <is>
           <t>Depreciation recapture risk?</t>
         </is>
       </c>
-      <c r="B13" s="57" t="inlineStr">
+      <c r="B13" s="58" t="inlineStr">
         <is>
           <t>"None"</t>
         </is>
       </c>
-      <c r="C13" s="57" t="inlineStr">
+      <c r="C13" s="58" t="inlineStr">
         <is>
           <t>"Yes (Sec 1250)"</t>
         </is>
       </c>
-      <c r="D13" s="57" t="inlineStr">
+      <c r="D13" s="58" t="inlineStr">
         <is>
           <t>""</t>
         </is>
       </c>
     </row>
     <row r="14" ht="20" customHeight="1">
-      <c r="A14" s="55" t="inlineStr">
+      <c r="A14" s="56" t="inlineStr">
         <is>
           <t>Loss carryover allowed?</t>
         </is>
       </c>
-      <c r="B14" s="57" t="inlineStr">
+      <c r="B14" s="58" t="inlineStr">
         <is>
           <t>"No"</t>
         </is>
       </c>
-      <c r="C14" s="57" t="inlineStr">
+      <c r="C14" s="58" t="inlineStr">
         <is>
           <t>"Yes"</t>
         </is>
       </c>
-      <c r="D14" s="57" t="inlineStr">
+      <c r="D14" s="58" t="inlineStr">
         <is>
           <t>""</t>
         </is>
       </c>
     </row>
     <row r="15" ht="20" customHeight="1">
-      <c r="A15" s="55" t="inlineStr">
+      <c r="A15" s="56" t="inlineStr">
         <is>
           <t>Recommended?</t>
         </is>
       </c>
-      <c r="B15" s="57">
+      <c r="B15" s="58">
         <f>IF(B12&gt;=C12,"✅ Pick this","")</f>
         <v/>
       </c>
-      <c r="C15" s="57">
+      <c r="C15" s="58">
         <f>IF(C12&gt;B12,"✅ Pick this","")</f>
         <v/>
       </c>
-      <c r="D15" s="57" t="inlineStr">
+      <c r="D15" s="58" t="inlineStr">
         <is>
           <t>""</t>
         </is>
       </c>
     </row>
     <row r="17" ht="36" customHeight="1">
-      <c r="A17" s="41" t="inlineStr">
+      <c r="A17" s="42" t="inlineStr">
         <is>
           <t>⚠ Actual-method depreciation locks the home's office-portion into Section 1250 unrecaptured-gain treatment if you sell — taxed at up to 25% on the depreciation recapture. Simplified avoids this. If you plan to sell the home within 5 years, the math often favors Simplified.</t>
         </is>
       </c>
     </row>
     <row r="19" ht="22" customHeight="1">
-      <c r="A19" s="42">
+      <c r="A19" s="43">
         <f>HYPERLINK("#'Space Allocation'!A5", "← Back: Space Allocation")</f>
         <v/>
       </c>
-      <c r="B19" s="43" t="n"/>
-      <c r="C19" s="43" t="n"/>
-      <c r="D19" s="43" t="n"/>
-      <c r="E19" s="43" t="n"/>
-      <c r="F19" s="43" t="n"/>
-      <c r="G19" s="42">
+      <c r="B19" s="44" t="n"/>
+      <c r="C19" s="44" t="n"/>
+      <c r="D19" s="44" t="n"/>
+      <c r="E19" s="44" t="n"/>
+      <c r="F19" s="44" t="n"/>
+      <c r="G19" s="43">
         <f>HYPERLINK("#'Actual Expenses'!A5", "Next: Actual Expenses →")</f>
         <v/>
       </c>
-      <c r="H19" s="43" t="n"/>
-      <c r="I19" s="43" t="n"/>
-      <c r="J19" s="43" t="n"/>
-      <c r="K19" s="43" t="n"/>
-      <c r="L19" s="43" t="n"/>
+      <c r="H19" s="44" t="n"/>
+      <c r="I19" s="44" t="n"/>
+      <c r="J19" s="44" t="n"/>
+      <c r="K19" s="44" t="n"/>
+      <c r="L19" s="44" t="n"/>
     </row>
     <row r="20" ht="22" customHeight="1">
-      <c r="A20" s="43" t="n"/>
-      <c r="B20" s="43" t="n"/>
-      <c r="C20" s="43" t="n"/>
-      <c r="D20" s="43" t="n"/>
-      <c r="E20" s="43" t="n"/>
-      <c r="F20" s="43" t="n"/>
-      <c r="G20" s="43" t="n"/>
-      <c r="H20" s="43" t="n"/>
-      <c r="I20" s="43" t="n"/>
-      <c r="J20" s="43" t="n"/>
-      <c r="K20" s="43" t="n"/>
-      <c r="L20" s="43" t="n"/>
+      <c r="A20" s="44" t="n"/>
+      <c r="B20" s="44" t="n"/>
+      <c r="C20" s="44" t="n"/>
+      <c r="D20" s="44" t="n"/>
+      <c r="E20" s="44" t="n"/>
+      <c r="F20" s="44" t="n"/>
+      <c r="G20" s="44" t="n"/>
+      <c r="H20" s="44" t="n"/>
+      <c r="I20" s="44" t="n"/>
+      <c r="J20" s="44" t="n"/>
+      <c r="K20" s="44" t="n"/>
+      <c r="L20" s="44" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="11">
@@ -2471,23 +2473,23 @@
       <c r="L1" s="1" t="n"/>
     </row>
     <row r="2" ht="28" customHeight="1">
-      <c r="A2" s="13">
+      <c r="A2" s="14">
         <f>HYPERLINK("#'Method Election'!A5", "← BACK")</f>
         <v/>
       </c>
-      <c r="B2" s="14" t="n"/>
-      <c r="C2" s="14" t="n"/>
-      <c r="D2" s="23" t="inlineStr">
+      <c r="B2" s="15" t="n"/>
+      <c r="C2" s="15" t="n"/>
+      <c r="D2" s="24" t="inlineStr">
         <is>
           <t>SECTION 4 OF 5</t>
         </is>
       </c>
-      <c r="J2" s="24">
+      <c r="J2" s="25">
         <f>HYPERLINK("#'STR Routing'!A5", "NEXT →")</f>
         <v/>
       </c>
-      <c r="K2" s="25" t="n"/>
-      <c r="L2" s="25" t="n"/>
+      <c r="K2" s="26" t="n"/>
+      <c r="L2" s="26" t="n"/>
     </row>
     <row r="3" ht="6" customHeight="1">
       <c r="A3" s="1" t="n"/>
@@ -2504,317 +2506,317 @@
       <c r="L3" s="1" t="n"/>
     </row>
     <row r="4" ht="36" customHeight="1">
-      <c r="A4" s="26" t="inlineStr">
+      <c r="A4" s="27" t="inlineStr">
         <is>
           <t>Actual Expenses</t>
         </is>
       </c>
     </row>
     <row r="5" ht="18" customHeight="1">
-      <c r="A5" s="27" t="inlineStr">
+      <c r="A5" s="28" t="inlineStr">
         <is>
           <t>Direct + indirect + depreciation. Indirect is allocated by business-use %.</t>
         </is>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="28" t="inlineStr">
+      <c r="A6" s="29" t="inlineStr">
         <is>
           <t>Fill the highlighted fields below.</t>
         </is>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1">
-      <c r="A7" s="29" t="inlineStr">
+      <c r="A7" s="30" t="inlineStr">
         <is>
           <t>ACTUAL EXPENSES</t>
         </is>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
-      <c r="A8" s="30" t="inlineStr">
+      <c r="A8" s="31" t="inlineStr">
         <is>
           <t>Direct repairs (only-office, 100% deductible):</t>
         </is>
       </c>
-      <c r="B8" s="58" t="n">
+      <c r="B8" s="59" t="n">
         <v>0</v>
       </c>
-      <c r="C8" s="32" t="n"/>
-      <c r="D8" s="32" t="n"/>
-      <c r="E8" s="32" t="n"/>
-      <c r="F8" s="32" t="n"/>
-      <c r="G8" s="32" t="n"/>
-      <c r="H8" s="32" t="n"/>
-      <c r="I8" s="32" t="n"/>
-      <c r="J8" s="32" t="n"/>
-      <c r="K8" s="32" t="n"/>
-      <c r="L8" s="33" t="n"/>
+      <c r="C8" s="33" t="n"/>
+      <c r="D8" s="33" t="n"/>
+      <c r="E8" s="33" t="n"/>
+      <c r="F8" s="33" t="n"/>
+      <c r="G8" s="33" t="n"/>
+      <c r="H8" s="33" t="n"/>
+      <c r="I8" s="33" t="n"/>
+      <c r="J8" s="33" t="n"/>
+      <c r="K8" s="33" t="n"/>
+      <c r="L8" s="34" t="n"/>
     </row>
     <row r="9" ht="22" customHeight="1">
-      <c r="A9" s="34" t="inlineStr">
+      <c r="A9" s="35" t="inlineStr">
         <is>
           <t>Indirect — Electric ($/yr):</t>
         </is>
       </c>
-      <c r="B9" s="59" t="n">
+      <c r="B9" s="60" t="n">
         <v>2400</v>
       </c>
-      <c r="C9" s="6" t="n"/>
-      <c r="D9" s="6" t="n"/>
-      <c r="E9" s="6" t="n"/>
-      <c r="F9" s="6" t="n"/>
-      <c r="G9" s="6" t="n"/>
-      <c r="H9" s="6" t="n"/>
-      <c r="I9" s="6" t="n"/>
-      <c r="J9" s="6" t="n"/>
-      <c r="K9" s="6" t="n"/>
-      <c r="L9" s="36" t="n"/>
+      <c r="C9" s="7" t="n"/>
+      <c r="D9" s="7" t="n"/>
+      <c r="E9" s="7" t="n"/>
+      <c r="F9" s="7" t="n"/>
+      <c r="G9" s="7" t="n"/>
+      <c r="H9" s="7" t="n"/>
+      <c r="I9" s="7" t="n"/>
+      <c r="J9" s="7" t="n"/>
+      <c r="K9" s="7" t="n"/>
+      <c r="L9" s="37" t="n"/>
     </row>
     <row r="10" ht="22" customHeight="1">
-      <c r="A10" s="34" t="inlineStr">
+      <c r="A10" s="35" t="inlineStr">
         <is>
           <t>Indirect — Gas ($/yr):</t>
         </is>
       </c>
-      <c r="B10" s="59" t="n">
+      <c r="B10" s="60" t="n">
         <v>980</v>
       </c>
-      <c r="C10" s="6" t="n"/>
-      <c r="D10" s="6" t="n"/>
-      <c r="E10" s="6" t="n"/>
-      <c r="F10" s="6" t="n"/>
-      <c r="G10" s="6" t="n"/>
-      <c r="H10" s="6" t="n"/>
-      <c r="I10" s="6" t="n"/>
-      <c r="J10" s="6" t="n"/>
-      <c r="K10" s="6" t="n"/>
-      <c r="L10" s="36" t="n"/>
+      <c r="C10" s="7" t="n"/>
+      <c r="D10" s="7" t="n"/>
+      <c r="E10" s="7" t="n"/>
+      <c r="F10" s="7" t="n"/>
+      <c r="G10" s="7" t="n"/>
+      <c r="H10" s="7" t="n"/>
+      <c r="I10" s="7" t="n"/>
+      <c r="J10" s="7" t="n"/>
+      <c r="K10" s="7" t="n"/>
+      <c r="L10" s="37" t="n"/>
     </row>
     <row r="11" ht="22" customHeight="1">
-      <c r="A11" s="34" t="inlineStr">
+      <c r="A11" s="35" t="inlineStr">
         <is>
           <t>Indirect — Water ($/yr):</t>
         </is>
       </c>
-      <c r="B11" s="59" t="n">
+      <c r="B11" s="60" t="n">
         <v>420</v>
       </c>
-      <c r="C11" s="6" t="n"/>
-      <c r="D11" s="6" t="n"/>
-      <c r="E11" s="6" t="n"/>
-      <c r="F11" s="6" t="n"/>
-      <c r="G11" s="6" t="n"/>
-      <c r="H11" s="6" t="n"/>
-      <c r="I11" s="6" t="n"/>
-      <c r="J11" s="6" t="n"/>
-      <c r="K11" s="6" t="n"/>
-      <c r="L11" s="36" t="n"/>
+      <c r="C11" s="7" t="n"/>
+      <c r="D11" s="7" t="n"/>
+      <c r="E11" s="7" t="n"/>
+      <c r="F11" s="7" t="n"/>
+      <c r="G11" s="7" t="n"/>
+      <c r="H11" s="7" t="n"/>
+      <c r="I11" s="7" t="n"/>
+      <c r="J11" s="7" t="n"/>
+      <c r="K11" s="7" t="n"/>
+      <c r="L11" s="37" t="n"/>
     </row>
     <row r="12" ht="22" customHeight="1">
-      <c r="A12" s="34" t="inlineStr">
+      <c r="A12" s="35" t="inlineStr">
         <is>
           <t>Indirect — Internet ($/yr):</t>
         </is>
       </c>
-      <c r="B12" s="59" t="n">
+      <c r="B12" s="60" t="n">
         <v>720</v>
       </c>
-      <c r="C12" s="6" t="n"/>
-      <c r="D12" s="6" t="n"/>
-      <c r="E12" s="6" t="n"/>
-      <c r="F12" s="6" t="n"/>
-      <c r="G12" s="6" t="n"/>
-      <c r="H12" s="6" t="n"/>
-      <c r="I12" s="6" t="n"/>
-      <c r="J12" s="6" t="n"/>
-      <c r="K12" s="6" t="n"/>
-      <c r="L12" s="36" t="n"/>
+      <c r="C12" s="7" t="n"/>
+      <c r="D12" s="7" t="n"/>
+      <c r="E12" s="7" t="n"/>
+      <c r="F12" s="7" t="n"/>
+      <c r="G12" s="7" t="n"/>
+      <c r="H12" s="7" t="n"/>
+      <c r="I12" s="7" t="n"/>
+      <c r="J12" s="7" t="n"/>
+      <c r="K12" s="7" t="n"/>
+      <c r="L12" s="37" t="n"/>
     </row>
     <row r="13" ht="22" customHeight="1">
-      <c r="A13" s="34" t="inlineStr">
+      <c r="A13" s="35" t="inlineStr">
         <is>
           <t>Indirect — Insurance ($/yr):</t>
         </is>
       </c>
-      <c r="B13" s="59" t="n">
+      <c r="B13" s="60" t="n">
         <v>1840</v>
       </c>
-      <c r="C13" s="6" t="n"/>
-      <c r="D13" s="6" t="n"/>
-      <c r="E13" s="6" t="n"/>
-      <c r="F13" s="6" t="n"/>
-      <c r="G13" s="6" t="n"/>
-      <c r="H13" s="6" t="n"/>
-      <c r="I13" s="6" t="n"/>
-      <c r="J13" s="6" t="n"/>
-      <c r="K13" s="6" t="n"/>
-      <c r="L13" s="36" t="n"/>
+      <c r="C13" s="7" t="n"/>
+      <c r="D13" s="7" t="n"/>
+      <c r="E13" s="7" t="n"/>
+      <c r="F13" s="7" t="n"/>
+      <c r="G13" s="7" t="n"/>
+      <c r="H13" s="7" t="n"/>
+      <c r="I13" s="7" t="n"/>
+      <c r="J13" s="7" t="n"/>
+      <c r="K13" s="7" t="n"/>
+      <c r="L13" s="37" t="n"/>
     </row>
     <row r="14" ht="22" customHeight="1">
-      <c r="A14" s="34" t="inlineStr">
+      <c r="A14" s="35" t="inlineStr">
         <is>
           <t>Indirect — Repairs (whole house):</t>
         </is>
       </c>
-      <c r="B14" s="59" t="n">
+      <c r="B14" s="60" t="n">
         <v>620</v>
       </c>
-      <c r="C14" s="6" t="n"/>
-      <c r="D14" s="6" t="n"/>
-      <c r="E14" s="6" t="n"/>
-      <c r="F14" s="6" t="n"/>
-      <c r="G14" s="6" t="n"/>
-      <c r="H14" s="6" t="n"/>
-      <c r="I14" s="6" t="n"/>
-      <c r="J14" s="6" t="n"/>
-      <c r="K14" s="6" t="n"/>
-      <c r="L14" s="36" t="n"/>
+      <c r="C14" s="7" t="n"/>
+      <c r="D14" s="7" t="n"/>
+      <c r="E14" s="7" t="n"/>
+      <c r="F14" s="7" t="n"/>
+      <c r="G14" s="7" t="n"/>
+      <c r="H14" s="7" t="n"/>
+      <c r="I14" s="7" t="n"/>
+      <c r="J14" s="7" t="n"/>
+      <c r="K14" s="7" t="n"/>
+      <c r="L14" s="37" t="n"/>
     </row>
     <row r="15" ht="22" customHeight="1">
-      <c r="A15" s="34" t="inlineStr">
+      <c r="A15" s="35" t="inlineStr">
         <is>
           <t>Indirect — Real estate tax:</t>
         </is>
       </c>
-      <c r="B15" s="59" t="n">
+      <c r="B15" s="60" t="n">
         <v>4800</v>
       </c>
-      <c r="C15" s="6" t="n"/>
-      <c r="D15" s="6" t="n"/>
-      <c r="E15" s="6" t="n"/>
-      <c r="F15" s="6" t="n"/>
-      <c r="G15" s="6" t="n"/>
-      <c r="H15" s="6" t="n"/>
-      <c r="I15" s="6" t="n"/>
-      <c r="J15" s="6" t="n"/>
-      <c r="K15" s="6" t="n"/>
-      <c r="L15" s="36" t="n"/>
+      <c r="C15" s="7" t="n"/>
+      <c r="D15" s="7" t="n"/>
+      <c r="E15" s="7" t="n"/>
+      <c r="F15" s="7" t="n"/>
+      <c r="G15" s="7" t="n"/>
+      <c r="H15" s="7" t="n"/>
+      <c r="I15" s="7" t="n"/>
+      <c r="J15" s="7" t="n"/>
+      <c r="K15" s="7" t="n"/>
+      <c r="L15" s="37" t="n"/>
     </row>
     <row r="16" ht="22" customHeight="1">
-      <c r="A16" s="34" t="inlineStr">
+      <c r="A16" s="35" t="inlineStr">
         <is>
           <t>Indirect — Mortgage interest:</t>
         </is>
       </c>
-      <c r="B16" s="59" t="n">
+      <c r="B16" s="60" t="n">
         <v>9800</v>
       </c>
-      <c r="C16" s="6" t="n"/>
-      <c r="D16" s="6" t="n"/>
-      <c r="E16" s="6" t="n"/>
-      <c r="F16" s="6" t="n"/>
-      <c r="G16" s="6" t="n"/>
-      <c r="H16" s="6" t="n"/>
-      <c r="I16" s="6" t="n"/>
-      <c r="J16" s="6" t="n"/>
-      <c r="K16" s="6" t="n"/>
-      <c r="L16" s="36" t="n"/>
+      <c r="C16" s="7" t="n"/>
+      <c r="D16" s="7" t="n"/>
+      <c r="E16" s="7" t="n"/>
+      <c r="F16" s="7" t="n"/>
+      <c r="G16" s="7" t="n"/>
+      <c r="H16" s="7" t="n"/>
+      <c r="I16" s="7" t="n"/>
+      <c r="J16" s="7" t="n"/>
+      <c r="K16" s="7" t="n"/>
+      <c r="L16" s="37" t="n"/>
     </row>
     <row r="17" ht="22" customHeight="1">
-      <c r="A17" s="37" t="inlineStr">
+      <c r="A17" s="38" t="inlineStr">
         <is>
           <t>Home depreciable basis (building only):</t>
         </is>
       </c>
-      <c r="B17" s="60" t="n">
+      <c r="B17" s="61" t="n">
         <v>312000</v>
       </c>
-      <c r="C17" s="39" t="n"/>
-      <c r="D17" s="39" t="n"/>
-      <c r="E17" s="39" t="n"/>
-      <c r="F17" s="39" t="n"/>
-      <c r="G17" s="39" t="n"/>
-      <c r="H17" s="39" t="n"/>
-      <c r="I17" s="39" t="n"/>
-      <c r="J17" s="39" t="n"/>
-      <c r="K17" s="39" t="n"/>
-      <c r="L17" s="40" t="n"/>
+      <c r="C17" s="40" t="n"/>
+      <c r="D17" s="40" t="n"/>
+      <c r="E17" s="40" t="n"/>
+      <c r="F17" s="40" t="n"/>
+      <c r="G17" s="40" t="n"/>
+      <c r="H17" s="40" t="n"/>
+      <c r="I17" s="40" t="n"/>
+      <c r="J17" s="40" t="n"/>
+      <c r="K17" s="40" t="n"/>
+      <c r="L17" s="41" t="n"/>
     </row>
     <row r="19" ht="20" customHeight="1">
-      <c r="A19" s="55" t="inlineStr">
+      <c r="A19" s="56" t="inlineStr">
         <is>
           <t>Total indirect (sum):</t>
         </is>
       </c>
-      <c r="B19" s="61">
+      <c r="B19" s="62">
         <f>SUM(B9:B16)</f>
         <v/>
       </c>
     </row>
     <row r="20" ht="20" customHeight="1">
-      <c r="A20" s="55" t="inlineStr">
+      <c r="A20" s="56" t="inlineStr">
         <is>
           <t>Indirect × business-use % (Form 8829 Line 22):</t>
         </is>
       </c>
-      <c r="B20" s="61">
+      <c r="B20" s="62">
         <f>B19*'Space Allocation'!B13</f>
         <v/>
       </c>
     </row>
     <row r="21" ht="20" customHeight="1">
-      <c r="A21" s="55" t="inlineStr">
+      <c r="A21" s="56" t="inlineStr">
         <is>
           <t>Annual depreciation (basis × biz % ÷ 39):</t>
         </is>
       </c>
-      <c r="B21" s="61">
+      <c r="B21" s="62">
         <f>B17*'Space Allocation'!B13/39</f>
         <v/>
       </c>
     </row>
     <row r="22" ht="20" customHeight="1">
-      <c r="A22" s="48" t="inlineStr">
+      <c r="A22" s="49" t="inlineStr">
         <is>
           <t>Direct + Indirect × biz% + Depreciation:</t>
         </is>
       </c>
-      <c r="B22" s="62">
+      <c r="B22" s="63">
         <f>B8+B20+B21</f>
         <v/>
       </c>
     </row>
     <row r="24" ht="36" customHeight="1">
-      <c r="A24" s="41" t="inlineStr">
+      <c r="A24" s="42" t="inlineStr">
         <is>
           <t>ⓘ Direct expenses (only the office) are 100% deductible. Indirect expenses (whole house) are deductible at the business-use % from the Space Allocation tab. Home depreciation = (basis × business-use %) ÷ 39 yrs.</t>
         </is>
       </c>
     </row>
     <row r="26" ht="22" customHeight="1">
-      <c r="A26" s="42">
+      <c r="A26" s="43">
         <f>HYPERLINK("#'Method Election'!A5", "← Back: Method Election")</f>
         <v/>
       </c>
-      <c r="B26" s="43" t="n"/>
-      <c r="C26" s="43" t="n"/>
-      <c r="D26" s="43" t="n"/>
-      <c r="E26" s="43" t="n"/>
-      <c r="F26" s="43" t="n"/>
-      <c r="G26" s="42">
+      <c r="B26" s="44" t="n"/>
+      <c r="C26" s="44" t="n"/>
+      <c r="D26" s="44" t="n"/>
+      <c r="E26" s="44" t="n"/>
+      <c r="F26" s="44" t="n"/>
+      <c r="G26" s="43">
         <f>HYPERLINK("#'STR Routing'!A5", "Next: STR Routing →")</f>
         <v/>
       </c>
-      <c r="H26" s="43" t="n"/>
-      <c r="I26" s="43" t="n"/>
-      <c r="J26" s="43" t="n"/>
-      <c r="K26" s="43" t="n"/>
-      <c r="L26" s="43" t="n"/>
+      <c r="H26" s="44" t="n"/>
+      <c r="I26" s="44" t="n"/>
+      <c r="J26" s="44" t="n"/>
+      <c r="K26" s="44" t="n"/>
+      <c r="L26" s="44" t="n"/>
     </row>
     <row r="27" ht="22" customHeight="1">
-      <c r="A27" s="43" t="n"/>
-      <c r="B27" s="43" t="n"/>
-      <c r="C27" s="43" t="n"/>
-      <c r="D27" s="43" t="n"/>
-      <c r="E27" s="43" t="n"/>
-      <c r="F27" s="43" t="n"/>
-      <c r="G27" s="43" t="n"/>
-      <c r="H27" s="43" t="n"/>
-      <c r="I27" s="43" t="n"/>
-      <c r="J27" s="43" t="n"/>
-      <c r="K27" s="43" t="n"/>
-      <c r="L27" s="43" t="n"/>
+      <c r="A27" s="44" t="n"/>
+      <c r="B27" s="44" t="n"/>
+      <c r="C27" s="44" t="n"/>
+      <c r="D27" s="44" t="n"/>
+      <c r="E27" s="44" t="n"/>
+      <c r="F27" s="44" t="n"/>
+      <c r="G27" s="44" t="n"/>
+      <c r="H27" s="44" t="n"/>
+      <c r="I27" s="44" t="n"/>
+      <c r="J27" s="44" t="n"/>
+      <c r="K27" s="44" t="n"/>
+      <c r="L27" s="44" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -2872,23 +2874,23 @@
       <c r="L1" s="1" t="n"/>
     </row>
     <row r="2" ht="28" customHeight="1">
-      <c r="A2" s="13">
+      <c r="A2" s="14">
         <f>HYPERLINK("#'Actual Expenses'!A5", "← BACK")</f>
         <v/>
       </c>
-      <c r="B2" s="14" t="n"/>
-      <c r="C2" s="14" t="n"/>
-      <c r="D2" s="23" t="inlineStr">
+      <c r="B2" s="15" t="n"/>
+      <c r="C2" s="15" t="n"/>
+      <c r="D2" s="24" t="inlineStr">
         <is>
           <t>SECTION 5 OF 5</t>
         </is>
       </c>
-      <c r="J2" s="24">
+      <c r="J2" s="25">
         <f>HYPERLINK("#'Form 8829 Map'!A5", "NEXT →")</f>
         <v/>
       </c>
-      <c r="K2" s="25" t="n"/>
-      <c r="L2" s="25" t="n"/>
+      <c r="K2" s="26" t="n"/>
+      <c r="L2" s="26" t="n"/>
     </row>
     <row r="3" ht="6" customHeight="1">
       <c r="A3" s="1" t="n"/>
@@ -2905,106 +2907,106 @@
       <c r="L3" s="1" t="n"/>
     </row>
     <row r="4" ht="36" customHeight="1">
-      <c r="A4" s="26" t="inlineStr">
+      <c r="A4" s="27" t="inlineStr">
         <is>
           <t>STR Routing</t>
         </is>
       </c>
     </row>
     <row r="5" ht="18" customHeight="1">
-      <c r="A5" s="27" t="inlineStr">
+      <c r="A5" s="28" t="inlineStr">
         <is>
           <t>Where the deduction lands on your tax return.</t>
         </is>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="28" t="inlineStr">
+      <c r="A6" s="29" t="inlineStr">
         <is>
           <t>Fill the highlighted fields below.</t>
         </is>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1">
-      <c r="A7" s="29" t="inlineStr">
+      <c r="A7" s="30" t="inlineStr">
         <is>
           <t>STR ROUTING</t>
         </is>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
-      <c r="A8" s="50" t="inlineStr">
+      <c r="A8" s="51" t="inlineStr">
         <is>
           <t>Schedule classification:</t>
         </is>
       </c>
-      <c r="B8" s="51" t="inlineStr">
+      <c r="B8" s="52" t="inlineStr">
         <is>
           <t>Schedule E (passive)</t>
         </is>
       </c>
-      <c r="C8" s="52" t="n"/>
-      <c r="D8" s="52" t="n"/>
-      <c r="E8" s="52" t="n"/>
-      <c r="F8" s="52" t="n"/>
-      <c r="G8" s="52" t="n"/>
-      <c r="H8" s="52" t="n"/>
-      <c r="I8" s="52" t="n"/>
-      <c r="J8" s="52" t="n"/>
-      <c r="K8" s="52" t="n"/>
-      <c r="L8" s="53" t="n"/>
+      <c r="C8" s="53" t="n"/>
+      <c r="D8" s="53" t="n"/>
+      <c r="E8" s="53" t="n"/>
+      <c r="F8" s="53" t="n"/>
+      <c r="G8" s="53" t="n"/>
+      <c r="H8" s="53" t="n"/>
+      <c r="I8" s="53" t="n"/>
+      <c r="J8" s="53" t="n"/>
+      <c r="K8" s="53" t="n"/>
+      <c r="L8" s="54" t="n"/>
     </row>
     <row r="10" ht="24" customHeight="1">
-      <c r="A10" s="48" t="inlineStr">
+      <c r="A10" s="49" t="inlineStr">
         <is>
           <t>Form line for your deduction:</t>
         </is>
       </c>
-      <c r="B10" s="63">
+      <c r="B10" s="64">
         <f>IF(B8="Schedule E (passive)","Schedule E Line 18a (Other) — describe as ""Home office""",IF(B8="Schedule C (active)","Schedule C Line 30 (via Form 8829)","Set classification above"))</f>
         <v/>
       </c>
     </row>
     <row r="12" ht="36" customHeight="1">
-      <c r="A12" s="41" t="inlineStr">
+      <c r="A12" s="42" t="inlineStr">
         <is>
           <t>Schedule E filers: deduction lands on Line 18a (Other) of Schedule E. Schedule C filers: deduction lands on Form 8829 → Line 30 of Schedule C. Both methods (Simplified and Actual) work for both Schedule E and C.</t>
         </is>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">
-      <c r="A14" s="42">
+      <c r="A14" s="43">
         <f>HYPERLINK("#'Actual Expenses'!A5", "← Back: Actual Expenses")</f>
         <v/>
       </c>
-      <c r="B14" s="43" t="n"/>
-      <c r="C14" s="43" t="n"/>
-      <c r="D14" s="43" t="n"/>
-      <c r="E14" s="43" t="n"/>
-      <c r="F14" s="43" t="n"/>
-      <c r="G14" s="42">
+      <c r="B14" s="44" t="n"/>
+      <c r="C14" s="44" t="n"/>
+      <c r="D14" s="44" t="n"/>
+      <c r="E14" s="44" t="n"/>
+      <c r="F14" s="44" t="n"/>
+      <c r="G14" s="43">
         <f>HYPERLINK("#'Form 8829 Map'!A5", "Next: Form 8829 Map →")</f>
         <v/>
       </c>
-      <c r="H14" s="43" t="n"/>
-      <c r="I14" s="43" t="n"/>
-      <c r="J14" s="43" t="n"/>
-      <c r="K14" s="43" t="n"/>
-      <c r="L14" s="43" t="n"/>
+      <c r="H14" s="44" t="n"/>
+      <c r="I14" s="44" t="n"/>
+      <c r="J14" s="44" t="n"/>
+      <c r="K14" s="44" t="n"/>
+      <c r="L14" s="44" t="n"/>
     </row>
     <row r="15" ht="22" customHeight="1">
-      <c r="A15" s="43" t="n"/>
-      <c r="B15" s="43" t="n"/>
-      <c r="C15" s="43" t="n"/>
-      <c r="D15" s="43" t="n"/>
-      <c r="E15" s="43" t="n"/>
-      <c r="F15" s="43" t="n"/>
-      <c r="G15" s="43" t="n"/>
-      <c r="H15" s="43" t="n"/>
-      <c r="I15" s="43" t="n"/>
-      <c r="J15" s="43" t="n"/>
-      <c r="K15" s="43" t="n"/>
-      <c r="L15" s="43" t="n"/>
+      <c r="A15" s="44" t="n"/>
+      <c r="B15" s="44" t="n"/>
+      <c r="C15" s="44" t="n"/>
+      <c r="D15" s="44" t="n"/>
+      <c r="E15" s="44" t="n"/>
+      <c r="F15" s="44" t="n"/>
+      <c r="G15" s="44" t="n"/>
+      <c r="H15" s="44" t="n"/>
+      <c r="I15" s="44" t="n"/>
+      <c r="J15" s="44" t="n"/>
+      <c r="K15" s="44" t="n"/>
+      <c r="L15" s="44" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="12">
@@ -3069,23 +3071,23 @@
       <c r="L1" s="1" t="n"/>
     </row>
     <row r="2" ht="28" customHeight="1">
-      <c r="A2" s="13">
+      <c r="A2" s="14">
         <f>HYPERLINK("#'STR Routing'!A1", "← BACK")</f>
         <v/>
       </c>
-      <c r="B2" s="14" t="n"/>
-      <c r="C2" s="14" t="n"/>
-      <c r="D2" s="64" t="inlineStr">
+      <c r="B2" s="15" t="n"/>
+      <c r="C2" s="15" t="n"/>
+      <c r="D2" s="65" t="inlineStr">
         <is>
           <t>FORM 8829 MAP</t>
         </is>
       </c>
-      <c r="J2" s="24">
+      <c r="J2" s="25">
         <f>HYPERLINK("#'Launch'!A1", "NEXT →")</f>
         <v/>
       </c>
-      <c r="K2" s="25" t="n"/>
-      <c r="L2" s="25" t="n"/>
+      <c r="K2" s="26" t="n"/>
+      <c r="L2" s="26" t="n"/>
     </row>
     <row r="3" ht="6" customHeight="1">
       <c r="A3" s="1" t="n"/>
@@ -3102,229 +3104,229 @@
       <c r="L3" s="1" t="n"/>
     </row>
     <row r="4" ht="18" customHeight="1">
-      <c r="A4" s="65" t="inlineStr">
+      <c r="A4" s="66" t="inlineStr">
         <is>
           <t>Print this tab — mirror of Form 8829 (Expenses for Business Use of Your Home).</t>
         </is>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1">
-      <c r="A5" s="54" t="inlineStr">
+      <c r="A5" s="55" t="inlineStr">
         <is>
           <t>Line</t>
         </is>
       </c>
-      <c r="B5" s="54" t="inlineStr">
+      <c r="B5" s="55" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="C5" s="54" t="inlineStr">
+      <c r="C5" s="55" t="inlineStr">
         <is>
           <t>Amount</t>
         </is>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="66" t="inlineStr">
+      <c r="A6" s="67" t="inlineStr">
         <is>
           <t xml:space="preserve">  Part I — BUSINESS-USE %</t>
         </is>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
-      <c r="A7" s="67" t="inlineStr">
+      <c r="A7" s="68" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B7" s="68" t="inlineStr">
+      <c r="B7" s="69" t="inlineStr">
         <is>
           <t>Office area (sqft)</t>
         </is>
       </c>
-      <c r="C7" s="69">
+      <c r="C7" s="70">
         <f>'Space Allocation'!B9</f>
         <v/>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
-      <c r="A8" s="67" t="inlineStr">
+      <c r="A8" s="68" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B8" s="68" t="inlineStr">
+      <c r="B8" s="69" t="inlineStr">
         <is>
           <t>Total home area (sqft)</t>
         </is>
       </c>
-      <c r="C8" s="69">
+      <c r="C8" s="70">
         <f>'Space Allocation'!B8</f>
         <v/>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
-      <c r="A9" s="67" t="inlineStr">
+      <c r="A9" s="68" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="B9" s="68" t="inlineStr">
+      <c r="B9" s="69" t="inlineStr">
         <is>
           <t>Business-use percentage</t>
         </is>
       </c>
-      <c r="C9" s="70">
+      <c r="C9" s="71">
         <f>'Space Allocation'!B13</f>
         <v/>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1">
-      <c r="A10" s="66" t="inlineStr">
+      <c r="A10" s="67" t="inlineStr">
         <is>
           <t xml:space="preserve">  Part II — EXPENSES</t>
         </is>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
-      <c r="A11" s="67" t="inlineStr">
+      <c r="A11" s="68" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="B11" s="68" t="inlineStr">
+      <c r="B11" s="69" t="inlineStr">
         <is>
           <t>Direct expenses</t>
         </is>
       </c>
-      <c r="C11" s="61">
+      <c r="C11" s="62">
         <f>'Actual Expenses'!B8</f>
         <v/>
       </c>
     </row>
     <row r="12" ht="18" customHeight="1">
-      <c r="A12" s="67" t="inlineStr">
+      <c r="A12" s="68" t="inlineStr">
         <is>
           <t>9-13</t>
         </is>
       </c>
-      <c r="B12" s="68" t="inlineStr">
+      <c r="B12" s="69" t="inlineStr">
         <is>
           <t>Indirect (utilities + ins. + repairs + RE tax + mortgage int.)</t>
         </is>
       </c>
-      <c r="C12" s="61">
+      <c r="C12" s="62">
         <f>'Actual Expenses'!B19</f>
         <v/>
       </c>
     </row>
     <row r="13" ht="18" customHeight="1">
-      <c r="A13" s="67" t="inlineStr">
+      <c r="A13" s="68" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="B13" s="68" t="inlineStr">
+      <c r="B13" s="69" t="inlineStr">
         <is>
           <t>Indirect × business-use %</t>
         </is>
       </c>
-      <c r="C13" s="61">
+      <c r="C13" s="62">
         <f>'Actual Expenses'!B20</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="18" customHeight="1">
-      <c r="A14" s="67" t="inlineStr">
+      <c r="A14" s="68" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="B14" s="68" t="inlineStr">
+      <c r="B14" s="69" t="inlineStr">
         <is>
           <t>Add lines 8 + 14 (operating exp.)</t>
         </is>
       </c>
-      <c r="C14" s="61">
+      <c r="C14" s="62">
         <f>C12+C14</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="22" customHeight="1">
-      <c r="A15" s="66" t="inlineStr">
+      <c r="A15" s="67" t="inlineStr">
         <is>
           <t xml:space="preserve">  Part III — DEPRECIATION</t>
         </is>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1">
-      <c r="A16" s="67" t="inlineStr">
+      <c r="A16" s="68" t="inlineStr">
         <is>
           <t>36</t>
         </is>
       </c>
-      <c r="B16" s="68" t="inlineStr">
+      <c r="B16" s="69" t="inlineStr">
         <is>
           <t>Annual depreciation (39-yr SL × biz %)</t>
         </is>
       </c>
-      <c r="C16" s="61">
+      <c r="C16" s="62">
         <f>'Actual Expenses'!B21</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="22" customHeight="1">
-      <c r="A17" s="66" t="inlineStr">
+      <c r="A17" s="67" t="inlineStr">
         <is>
           <t xml:space="preserve">  Part IV — TOTAL</t>
         </is>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
-      <c r="A18" s="67" t="inlineStr"/>
-      <c r="B18" s="71" t="inlineStr">
+      <c r="A18" s="68" t="inlineStr"/>
+      <c r="B18" s="72" t="inlineStr">
         <is>
           <t>TOTAL ACTUAL DEDUCTION</t>
         </is>
       </c>
-      <c r="C18" s="72">
+      <c r="C18" s="73">
         <f>'Actual Expenses'!B22</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="18" customHeight="1">
-      <c r="A19" s="67" t="inlineStr"/>
-      <c r="B19" s="71" t="inlineStr">
+      <c r="A19" s="68" t="inlineStr"/>
+      <c r="B19" s="72" t="inlineStr">
         <is>
           <t>TOTAL SIMPLIFIED DEDUCTION</t>
         </is>
       </c>
-      <c r="C19" s="72">
+      <c r="C19" s="73">
         <f>MIN('Space Allocation'!B9,300)*5</f>
         <v/>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1">
-      <c r="A20" s="67" t="inlineStr"/>
-      <c r="B20" s="68" t="inlineStr">
+      <c r="A20" s="68" t="inlineStr"/>
+      <c r="B20" s="69" t="inlineStr">
         <is>
           <t>ELECTED METHOD</t>
         </is>
       </c>
-      <c r="C20" s="73">
+      <c r="C20" s="74">
         <f>'Method Election'!B8</f>
         <v/>
       </c>
     </row>
     <row r="21" ht="18" customHeight="1">
-      <c r="A21" s="67" t="inlineStr"/>
-      <c r="B21" s="71" t="inlineStr">
+      <c r="A21" s="68" t="inlineStr"/>
+      <c r="B21" s="72" t="inlineStr">
         <is>
           <t>FINAL DEDUCTION</t>
         </is>
       </c>
-      <c r="C21" s="72">
+      <c r="C21" s="73">
         <f>IF('Method Election'!B8="Simplified",MIN('Space Allocation'!B9,300)*5,IF('Method Election'!B8="Actual",'Actual Expenses'!B22,0))</f>
         <v/>
       </c>
@@ -3384,13 +3386,13 @@
       <c r="L1" s="1" t="n"/>
     </row>
     <row r="2" ht="28" customHeight="1">
-      <c r="A2" s="13">
+      <c r="A2" s="14">
         <f>HYPERLINK("#'Form 8829 Map'!A1", "← BACK")</f>
         <v/>
       </c>
-      <c r="B2" s="14" t="n"/>
-      <c r="C2" s="14" t="n"/>
-      <c r="D2" s="64" t="inlineStr">
+      <c r="B2" s="15" t="n"/>
+      <c r="C2" s="15" t="n"/>
+      <c r="D2" s="65" t="inlineStr">
         <is>
           <t>LAUNCH</t>
         </is>
@@ -3411,14 +3413,14 @@
       <c r="L3" s="1" t="n"/>
     </row>
     <row r="4" ht="42" customHeight="1">
-      <c r="A4" s="74" t="inlineStr">
+      <c r="A4" s="75" t="inlineStr">
         <is>
           <t>Your home-office deduction</t>
         </is>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1">
-      <c r="A5" s="27" t="inlineStr">
+      <c r="A5" s="28" t="inlineStr">
         <is>
           <t>Print the Form 8829 Map and route per your filing schedule.</t>
         </is>
@@ -3439,225 +3441,225 @@
       <c r="L6" s="1" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="6" t="n"/>
-      <c r="B8" s="6" t="n"/>
-      <c r="C8" s="6" t="n"/>
-      <c r="D8" s="6" t="n"/>
-      <c r="E8" s="6" t="n"/>
-      <c r="F8" s="6" t="n"/>
-      <c r="G8" s="6" t="n"/>
-      <c r="H8" s="6" t="n"/>
-      <c r="I8" s="6" t="n"/>
-      <c r="J8" s="6" t="n"/>
-      <c r="K8" s="6" t="n"/>
-      <c r="L8" s="6" t="n"/>
+      <c r="A8" s="7" t="n"/>
+      <c r="B8" s="7" t="n"/>
+      <c r="C8" s="7" t="n"/>
+      <c r="D8" s="7" t="n"/>
+      <c r="E8" s="7" t="n"/>
+      <c r="F8" s="7" t="n"/>
+      <c r="G8" s="7" t="n"/>
+      <c r="H8" s="7" t="n"/>
+      <c r="I8" s="7" t="n"/>
+      <c r="J8" s="7" t="n"/>
+      <c r="K8" s="7" t="n"/>
+      <c r="L8" s="7" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="75" t="inlineStr">
+      <c r="A9" s="76" t="inlineStr">
         <is>
           <t>FINAL DEDUCTION</t>
         </is>
       </c>
-      <c r="B9" s="76" t="n"/>
-      <c r="C9" s="76" t="n"/>
-      <c r="D9" s="77" t="n"/>
-      <c r="E9" s="78" t="inlineStr">
+      <c r="B9" s="77" t="n"/>
+      <c r="C9" s="77" t="n"/>
+      <c r="D9" s="78" t="n"/>
+      <c r="E9" s="79" t="inlineStr">
         <is>
           <t>METHOD</t>
         </is>
       </c>
-      <c r="F9" s="76" t="n"/>
-      <c r="G9" s="76" t="n"/>
-      <c r="H9" s="77" t="n"/>
-      <c r="I9" s="78" t="inlineStr">
+      <c r="F9" s="77" t="n"/>
+      <c r="G9" s="77" t="n"/>
+      <c r="H9" s="78" t="n"/>
+      <c r="I9" s="79" t="inlineStr">
         <is>
           <t>SCHEDULE</t>
         </is>
       </c>
-      <c r="J9" s="76" t="n"/>
-      <c r="K9" s="76" t="n"/>
-      <c r="L9" s="77" t="n"/>
+      <c r="J9" s="77" t="n"/>
+      <c r="K9" s="77" t="n"/>
+      <c r="L9" s="78" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="79">
+      <c r="A10" s="80">
         <f>IF('Method Election'!B8="Simplified",MIN('Space Allocation'!B9,300)*5,IF('Method Election'!B8="Actual",'Actual Expenses'!B22,0))</f>
         <v/>
       </c>
-      <c r="B10" s="80" t="n"/>
-      <c r="C10" s="80" t="n"/>
-      <c r="D10" s="81" t="n"/>
-      <c r="E10" s="82">
+      <c r="B10" s="81" t="n"/>
+      <c r="C10" s="81" t="n"/>
+      <c r="D10" s="82" t="n"/>
+      <c r="E10" s="83">
         <f>'Method Election'!B8</f>
         <v/>
       </c>
-      <c r="F10" s="80" t="n"/>
-      <c r="G10" s="80" t="n"/>
-      <c r="H10" s="81" t="n"/>
-      <c r="I10" s="83">
+      <c r="F10" s="81" t="n"/>
+      <c r="G10" s="81" t="n"/>
+      <c r="H10" s="82" t="n"/>
+      <c r="I10" s="84">
         <f>'STR Routing'!B8</f>
         <v/>
       </c>
-      <c r="J10" s="80" t="n"/>
-      <c r="K10" s="80" t="n"/>
-      <c r="L10" s="81" t="n"/>
+      <c r="J10" s="81" t="n"/>
+      <c r="K10" s="81" t="n"/>
+      <c r="L10" s="82" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="84" t="n"/>
-      <c r="B11" s="80" t="n"/>
-      <c r="C11" s="80" t="n"/>
-      <c r="D11" s="81" t="n"/>
-      <c r="E11" s="84" t="n"/>
-      <c r="F11" s="80" t="n"/>
-      <c r="G11" s="80" t="n"/>
-      <c r="H11" s="81" t="n"/>
-      <c r="I11" s="84" t="n"/>
-      <c r="J11" s="80" t="n"/>
-      <c r="K11" s="80" t="n"/>
-      <c r="L11" s="81" t="n"/>
+      <c r="A11" s="85" t="n"/>
+      <c r="B11" s="81" t="n"/>
+      <c r="C11" s="81" t="n"/>
+      <c r="D11" s="82" t="n"/>
+      <c r="E11" s="85" t="n"/>
+      <c r="F11" s="81" t="n"/>
+      <c r="G11" s="81" t="n"/>
+      <c r="H11" s="82" t="n"/>
+      <c r="I11" s="85" t="n"/>
+      <c r="J11" s="81" t="n"/>
+      <c r="K11" s="81" t="n"/>
+      <c r="L11" s="82" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="85" t="inlineStr">
+      <c r="A12" s="86" t="inlineStr">
         <is>
           <t>this tax year</t>
         </is>
       </c>
-      <c r="B12" s="86" t="n"/>
-      <c r="C12" s="86" t="n"/>
-      <c r="D12" s="87" t="n"/>
-      <c r="E12" s="85" t="inlineStr">
+      <c r="B12" s="87" t="n"/>
+      <c r="C12" s="87" t="n"/>
+      <c r="D12" s="88" t="n"/>
+      <c r="E12" s="86" t="inlineStr">
         <is>
           <t>elected for this year</t>
         </is>
       </c>
-      <c r="F12" s="86" t="n"/>
-      <c r="G12" s="86" t="n"/>
-      <c r="H12" s="87" t="n"/>
-      <c r="I12" s="85" t="inlineStr">
+      <c r="F12" s="87" t="n"/>
+      <c r="G12" s="87" t="n"/>
+      <c r="H12" s="88" t="n"/>
+      <c r="I12" s="86" t="inlineStr">
         <is>
           <t>where it lands</t>
         </is>
       </c>
-      <c r="J12" s="86" t="n"/>
-      <c r="K12" s="86" t="n"/>
-      <c r="L12" s="87" t="n"/>
+      <c r="J12" s="87" t="n"/>
+      <c r="K12" s="87" t="n"/>
+      <c r="L12" s="88" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="6" t="n"/>
-      <c r="B13" s="6" t="n"/>
-      <c r="C13" s="6" t="n"/>
-      <c r="D13" s="6" t="n"/>
-      <c r="E13" s="6" t="n"/>
-      <c r="F13" s="6" t="n"/>
-      <c r="G13" s="6" t="n"/>
-      <c r="H13" s="6" t="n"/>
-      <c r="I13" s="6" t="n"/>
-      <c r="J13" s="6" t="n"/>
-      <c r="K13" s="6" t="n"/>
-      <c r="L13" s="6" t="n"/>
+      <c r="A13" s="7" t="n"/>
+      <c r="B13" s="7" t="n"/>
+      <c r="C13" s="7" t="n"/>
+      <c r="D13" s="7" t="n"/>
+      <c r="E13" s="7" t="n"/>
+      <c r="F13" s="7" t="n"/>
+      <c r="G13" s="7" t="n"/>
+      <c r="H13" s="7" t="n"/>
+      <c r="I13" s="7" t="n"/>
+      <c r="J13" s="7" t="n"/>
+      <c r="K13" s="7" t="n"/>
+      <c r="L13" s="7" t="n"/>
     </row>
     <row r="16" ht="24" customHeight="1">
-      <c r="A16" s="13">
+      <c r="A16" s="14">
         <f>HYPERLINK("#'Form 8829 Map'!A1", "📄  PRINT FORM 8829 MAP  →")</f>
         <v/>
       </c>
-      <c r="B16" s="14" t="n"/>
-      <c r="C16" s="14" t="n"/>
-      <c r="D16" s="14" t="n"/>
-      <c r="E16" s="14" t="n"/>
-      <c r="F16" s="14" t="n"/>
-      <c r="G16" s="14" t="n"/>
-      <c r="H16" s="14" t="n"/>
-      <c r="I16" s="14" t="n"/>
-      <c r="J16" s="14" t="n"/>
-      <c r="K16" s="14" t="n"/>
-      <c r="L16" s="14" t="n"/>
+      <c r="B16" s="15" t="n"/>
+      <c r="C16" s="15" t="n"/>
+      <c r="D16" s="15" t="n"/>
+      <c r="E16" s="15" t="n"/>
+      <c r="F16" s="15" t="n"/>
+      <c r="G16" s="15" t="n"/>
+      <c r="H16" s="15" t="n"/>
+      <c r="I16" s="15" t="n"/>
+      <c r="J16" s="15" t="n"/>
+      <c r="K16" s="15" t="n"/>
+      <c r="L16" s="15" t="n"/>
     </row>
     <row r="17" ht="24" customHeight="1">
-      <c r="A17" s="14" t="n"/>
-      <c r="B17" s="14" t="n"/>
-      <c r="C17" s="14" t="n"/>
-      <c r="D17" s="14" t="n"/>
-      <c r="E17" s="14" t="n"/>
-      <c r="F17" s="14" t="n"/>
-      <c r="G17" s="14" t="n"/>
-      <c r="H17" s="14" t="n"/>
-      <c r="I17" s="14" t="n"/>
-      <c r="J17" s="14" t="n"/>
-      <c r="K17" s="14" t="n"/>
-      <c r="L17" s="14" t="n"/>
+      <c r="A17" s="15" t="n"/>
+      <c r="B17" s="15" t="n"/>
+      <c r="C17" s="15" t="n"/>
+      <c r="D17" s="15" t="n"/>
+      <c r="E17" s="15" t="n"/>
+      <c r="F17" s="15" t="n"/>
+      <c r="G17" s="15" t="n"/>
+      <c r="H17" s="15" t="n"/>
+      <c r="I17" s="15" t="n"/>
+      <c r="J17" s="15" t="n"/>
+      <c r="K17" s="15" t="n"/>
+      <c r="L17" s="15" t="n"/>
     </row>
     <row r="18" ht="24" customHeight="1">
-      <c r="A18" s="14" t="n"/>
-      <c r="B18" s="14" t="n"/>
-      <c r="C18" s="14" t="n"/>
-      <c r="D18" s="14" t="n"/>
-      <c r="E18" s="14" t="n"/>
-      <c r="F18" s="14" t="n"/>
-      <c r="G18" s="14" t="n"/>
-      <c r="H18" s="14" t="n"/>
-      <c r="I18" s="14" t="n"/>
-      <c r="J18" s="14" t="n"/>
-      <c r="K18" s="14" t="n"/>
-      <c r="L18" s="14" t="n"/>
+      <c r="A18" s="15" t="n"/>
+      <c r="B18" s="15" t="n"/>
+      <c r="C18" s="15" t="n"/>
+      <c r="D18" s="15" t="n"/>
+      <c r="E18" s="15" t="n"/>
+      <c r="F18" s="15" t="n"/>
+      <c r="G18" s="15" t="n"/>
+      <c r="H18" s="15" t="n"/>
+      <c r="I18" s="15" t="n"/>
+      <c r="J18" s="15" t="n"/>
+      <c r="K18" s="15" t="n"/>
+      <c r="L18" s="15" t="n"/>
     </row>
     <row r="19" ht="24" customHeight="1">
-      <c r="A19" s="14" t="n"/>
-      <c r="B19" s="14" t="n"/>
-      <c r="C19" s="14" t="n"/>
-      <c r="D19" s="14" t="n"/>
-      <c r="E19" s="14" t="n"/>
-      <c r="F19" s="14" t="n"/>
-      <c r="G19" s="14" t="n"/>
-      <c r="H19" s="14" t="n"/>
-      <c r="I19" s="14" t="n"/>
-      <c r="J19" s="14" t="n"/>
-      <c r="K19" s="14" t="n"/>
-      <c r="L19" s="14" t="n"/>
+      <c r="A19" s="15" t="n"/>
+      <c r="B19" s="15" t="n"/>
+      <c r="C19" s="15" t="n"/>
+      <c r="D19" s="15" t="n"/>
+      <c r="E19" s="15" t="n"/>
+      <c r="F19" s="15" t="n"/>
+      <c r="G19" s="15" t="n"/>
+      <c r="H19" s="15" t="n"/>
+      <c r="I19" s="15" t="n"/>
+      <c r="J19" s="15" t="n"/>
+      <c r="K19" s="15" t="n"/>
+      <c r="L19" s="15" t="n"/>
     </row>
     <row r="20" ht="24" customHeight="1">
-      <c r="A20" s="14" t="n"/>
-      <c r="B20" s="14" t="n"/>
-      <c r="C20" s="14" t="n"/>
-      <c r="D20" s="14" t="n"/>
-      <c r="E20" s="14" t="n"/>
-      <c r="F20" s="14" t="n"/>
-      <c r="G20" s="14" t="n"/>
-      <c r="H20" s="14" t="n"/>
-      <c r="I20" s="14" t="n"/>
-      <c r="J20" s="14" t="n"/>
-      <c r="K20" s="14" t="n"/>
-      <c r="L20" s="14" t="n"/>
+      <c r="A20" s="15" t="n"/>
+      <c r="B20" s="15" t="n"/>
+      <c r="C20" s="15" t="n"/>
+      <c r="D20" s="15" t="n"/>
+      <c r="E20" s="15" t="n"/>
+      <c r="F20" s="15" t="n"/>
+      <c r="G20" s="15" t="n"/>
+      <c r="H20" s="15" t="n"/>
+      <c r="I20" s="15" t="n"/>
+      <c r="J20" s="15" t="n"/>
+      <c r="K20" s="15" t="n"/>
+      <c r="L20" s="15" t="n"/>
     </row>
     <row r="23" ht="36" customHeight="1">
-      <c r="A23" s="88" t="inlineStr">
+      <c r="A23" s="89" t="inlineStr">
         <is>
           <t>💡 Upgrade to the Tax Season Bundle ($147) at thestrledger.com/tax-bundle.</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="20" t="n"/>
-      <c r="B25" s="20" t="n"/>
-      <c r="C25" s="20" t="n"/>
-      <c r="D25" s="20" t="n"/>
-      <c r="E25" s="20" t="n"/>
-      <c r="F25" s="20" t="n"/>
-      <c r="G25" s="20" t="n"/>
-      <c r="H25" s="20" t="n"/>
-      <c r="I25" s="20" t="n"/>
-      <c r="J25" s="20" t="n"/>
-      <c r="K25" s="20" t="n"/>
-      <c r="L25" s="20" t="n"/>
+      <c r="A25" s="21" t="n"/>
+      <c r="B25" s="21" t="n"/>
+      <c r="C25" s="21" t="n"/>
+      <c r="D25" s="21" t="n"/>
+      <c r="E25" s="21" t="n"/>
+      <c r="F25" s="21" t="n"/>
+      <c r="G25" s="21" t="n"/>
+      <c r="H25" s="21" t="n"/>
+      <c r="I25" s="21" t="n"/>
+      <c r="J25" s="21" t="n"/>
+      <c r="K25" s="21" t="n"/>
+      <c r="L25" s="21" t="n"/>
     </row>
     <row r="26" ht="18" customHeight="1">
-      <c r="A26" s="21" t="inlineStr">
+      <c r="A26" s="22" t="inlineStr">
         <is>
           <t>Questions? hello@thestrledger.com</t>
         </is>
       </c>
     </row>
     <row r="27" ht="18" customHeight="1">
-      <c r="A27" s="22" t="inlineStr">
+      <c r="A27" s="23" t="inlineStr">
         <is>
           <t>TAX-006 · v2.2 · Free updates forever</t>
         </is>
@@ -3727,13 +3729,13 @@
       <c r="L1" s="1" t="n"/>
     </row>
     <row r="2" ht="28" customHeight="1">
-      <c r="A2" s="13">
+      <c r="A2" s="14">
         <f>HYPERLINK("#'Launch'!A1", "← BACK")</f>
         <v/>
       </c>
-      <c r="B2" s="14" t="n"/>
-      <c r="C2" s="14" t="n"/>
-      <c r="D2" s="64" t="inlineStr">
+      <c r="B2" s="15" t="n"/>
+      <c r="C2" s="15" t="n"/>
+      <c r="D2" s="65" t="inlineStr">
         <is>
           <t>SETTINGS</t>
         </is>
@@ -3754,149 +3756,149 @@
       <c r="L3" s="1" t="n"/>
     </row>
     <row r="4" ht="18" customHeight="1">
-      <c r="A4" s="65" t="inlineStr">
+      <c r="A4" s="66" t="inlineStr">
         <is>
           <t>Active tax year · references</t>
         </is>
       </c>
     </row>
     <row r="5" ht="18" customHeight="1">
-      <c r="A5" s="89" t="inlineStr">
+      <c r="A5" s="90" t="inlineStr">
         <is>
           <t>Active tax year:</t>
         </is>
       </c>
-      <c r="B5" s="90" t="n">
+      <c r="B5" s="91" t="n">
         <v>2026</v>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
-      <c r="A6" s="89" t="inlineStr">
+      <c r="A6" s="90" t="inlineStr">
         <is>
           <t>Simplified-method rate ($/sqft):</t>
         </is>
       </c>
-      <c r="B6" s="91" t="n">
+      <c r="B6" s="92" t="n">
         <v>5</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
-      <c r="A7" s="89" t="inlineStr">
+      <c r="A7" s="90" t="inlineStr">
         <is>
           <t>Simplified-method sqft cap:</t>
         </is>
       </c>
-      <c r="B7" s="92" t="n">
+      <c r="B7" s="93" t="n">
         <v>300</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
-      <c r="A8" s="89" t="inlineStr">
+      <c r="A8" s="90" t="inlineStr">
         <is>
           <t>Home depreciation life (yr):</t>
         </is>
       </c>
-      <c r="B8" s="93" t="n">
+      <c r="B8" s="94" t="n">
         <v>39</v>
       </c>
     </row>
     <row r="10" ht="8" customHeight="1"/>
     <row r="11" ht="22" customHeight="1">
-      <c r="A11" s="94" t="inlineStr">
+      <c r="A11" s="95" t="inlineStr">
         <is>
           <t>Year-end Archive</t>
         </is>
       </c>
     </row>
     <row r="12" ht="18" customHeight="1">
-      <c r="A12" s="54" t="inlineStr">
+      <c r="A12" s="55" t="inlineStr">
         <is>
           <t>Year</t>
         </is>
       </c>
-      <c r="B12" s="54" t="inlineStr">
+      <c r="B12" s="55" t="inlineStr">
         <is>
           <t>Method</t>
         </is>
       </c>
-      <c r="C12" s="54" t="inlineStr">
+      <c r="C12" s="55" t="inlineStr">
         <is>
           <t>Deduction ($)</t>
         </is>
       </c>
     </row>
     <row r="13" ht="16" customHeight="1">
-      <c r="A13" s="95" t="n">
+      <c r="A13" s="96" t="n">
         <v>2024</v>
       </c>
-      <c r="B13" s="93" t="n"/>
-      <c r="C13" s="96" t="n"/>
+      <c r="B13" s="94" t="n"/>
+      <c r="C13" s="97" t="n"/>
     </row>
     <row r="14" ht="16" customHeight="1">
-      <c r="A14" s="95" t="n">
+      <c r="A14" s="96" t="n">
         <v>2025</v>
       </c>
-      <c r="B14" s="93" t="n"/>
-      <c r="C14" s="96" t="n"/>
+      <c r="B14" s="94" t="n"/>
+      <c r="C14" s="97" t="n"/>
     </row>
     <row r="15" ht="16" customHeight="1">
-      <c r="A15" s="95" t="n">
+      <c r="A15" s="96" t="n">
         <v>2026</v>
       </c>
-      <c r="B15" s="93" t="n"/>
-      <c r="C15" s="96" t="n"/>
+      <c r="B15" s="94" t="n"/>
+      <c r="C15" s="97" t="n"/>
     </row>
     <row r="16" ht="16" customHeight="1">
-      <c r="A16" s="95" t="n">
+      <c r="A16" s="96" t="n">
         <v>2027</v>
       </c>
-      <c r="B16" s="93" t="n"/>
-      <c r="C16" s="96" t="n"/>
+      <c r="B16" s="94" t="n"/>
+      <c r="C16" s="97" t="n"/>
     </row>
     <row r="17" ht="16" customHeight="1">
-      <c r="A17" s="95" t="n">
+      <c r="A17" s="96" t="n">
         <v>2028</v>
       </c>
-      <c r="B17" s="93" t="n"/>
-      <c r="C17" s="96" t="n"/>
+      <c r="B17" s="94" t="n"/>
+      <c r="C17" s="97" t="n"/>
     </row>
     <row r="18" ht="16" customHeight="1">
-      <c r="A18" s="95" t="n">
+      <c r="A18" s="96" t="n">
         <v>2029</v>
       </c>
-      <c r="B18" s="93" t="n"/>
-      <c r="C18" s="96" t="n"/>
+      <c r="B18" s="94" t="n"/>
+      <c r="C18" s="97" t="n"/>
     </row>
     <row r="19" ht="16" customHeight="1">
-      <c r="A19" s="95" t="n">
+      <c r="A19" s="96" t="n">
         <v>2030</v>
       </c>
-      <c r="B19" s="93" t="n"/>
-      <c r="C19" s="96" t="n"/>
+      <c r="B19" s="94" t="n"/>
+      <c r="C19" s="97" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="20" t="n"/>
-      <c r="B22" s="20" t="n"/>
-      <c r="C22" s="20" t="n"/>
-      <c r="D22" s="20" t="n"/>
-      <c r="E22" s="20" t="n"/>
-      <c r="F22" s="20" t="n"/>
-      <c r="G22" s="20" t="n"/>
-      <c r="H22" s="20" t="n"/>
-      <c r="I22" s="20" t="n"/>
-      <c r="J22" s="20" t="n"/>
-      <c r="K22" s="20" t="n"/>
-      <c r="L22" s="20" t="n"/>
+      <c r="A22" s="21" t="n"/>
+      <c r="B22" s="21" t="n"/>
+      <c r="C22" s="21" t="n"/>
+      <c r="D22" s="21" t="n"/>
+      <c r="E22" s="21" t="n"/>
+      <c r="F22" s="21" t="n"/>
+      <c r="G22" s="21" t="n"/>
+      <c r="H22" s="21" t="n"/>
+      <c r="I22" s="21" t="n"/>
+      <c r="J22" s="21" t="n"/>
+      <c r="K22" s="21" t="n"/>
+      <c r="L22" s="21" t="n"/>
     </row>
     <row r="23" ht="18" customHeight="1">
-      <c r="A23" s="21" t="inlineStr">
+      <c r="A23" s="22" t="inlineStr">
         <is>
           <t>Questions? hello@thestrledger.com</t>
         </is>
       </c>
     </row>
     <row r="24" ht="18" customHeight="1">
-      <c r="A24" s="22" t="inlineStr">
+      <c r="A24" s="23" t="inlineStr">
         <is>
           <t>TAX-006 · v2.2 · Free updates forever</t>
         </is>
